--- a/자료/3. 프로젝트_WBS.xlsx
+++ b/자료/3. 프로젝트_WBS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junse\Desktop\vscode\team-project\클라우드 서버 기반 보행영상 AI분석 ((주)비엔티코리아)\프로젝트 산출물 예시안\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junse\Desktop\vscode\team-project\ONEPIC\자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B590228-D570-4941-B54D-6EF0A930596A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE99B49-84D9-4440-A00D-D84D3232A080}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="116">
   <si>
     <t>Project</t>
   </si>
@@ -481,14 +481,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>서버 구축</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>기초틀 구성</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>19~21 일본</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -501,8 +493,48 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
+    <t>서버 구축 및 기초틀 구성</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>F/E - B/E 연동</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.4</t>
+  </si>
+  <si>
+    <t>3.2.5</t>
+  </si>
+  <si>
+    <t>AI - B/E 연동</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t>UI 디자인</t>
+      <t>DB -  B/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 연동</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.6</t>
+  </si>
+  <si>
+    <t>AI 객체 이미지 수집 및 레이블링</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">UI </t>
     </r>
     <r>
       <rPr>
@@ -512,8 +544,15 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> - 컬러, 타이포그래피</t>
+      <t>디자인 - 컬러, 타이포그래피</t>
     </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.4.5</t>
+  </si>
+  <si>
+    <t>객체 레이블링</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -526,7 +565,7 @@
     <numFmt numFmtId="177" formatCode="m&quot;/&quot;d"/>
     <numFmt numFmtId="178" formatCode="m&quot;월&quot;\ d&quot;일&quot;"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -703,12 +742,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -844,6 +888,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB2FF7D"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -1339,7 +1389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1400,132 +1450,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1562,41 +1486,11 @@
     <xf numFmtId="178" fontId="23" fillId="14" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="23" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="23" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="15" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1622,13 +1516,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1646,28 +1534,7 @@
     <xf numFmtId="0" fontId="13" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="16" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1687,15 +1554,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1721,12 +1579,6 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1739,12 +1591,6 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1754,16 +1600,7 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1775,22 +1612,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1820,12 +1642,6 @@
     <xf numFmtId="178" fontId="21" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="21" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="21" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1844,12 +1660,6 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1862,6 +1672,252 @@
     <xf numFmtId="0" fontId="21" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="15" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="23" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="23" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="16" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1870,6 +1926,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF00FFFF"/>
       <color rgb="FFB2FF7D"/>
       <color rgb="FFD29BFB"/>
       <color rgb="FFC6EDFA"/>
@@ -2086,7 +2143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE1009"/>
+  <dimension ref="A1:AE1014"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -2106,12 +2163,12 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="146" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
       <c r="F1" s="11"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
@@ -2142,12 +2199,12 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
       <c r="F2" s="2" t="s">
         <v>72</v>
       </c>
@@ -2179,13 +2236,13 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="62" t="s">
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="20" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="3"/>
@@ -2217,11 +2274,11 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="67" t="s">
+      <c r="B4" s="149"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="25" t="s">
         <v>74</v>
       </c>
       <c r="G4" s="3"/>
@@ -2251,11 +2308,11 @@
       <c r="A5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="68" t="s">
+      <c r="B5" s="150"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="26" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="10"/>
@@ -2283,10 +2340,10 @@
     </row>
     <row r="6" spans="1:31" ht="18.75" customHeight="1">
       <c r="A6" s="12"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="151"/>
+      <c r="D6" s="151"/>
+      <c r="E6" s="151"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -2313,10 +2370,10 @@
     </row>
     <row r="7" spans="1:31" ht="18.75" customHeight="1">
       <c r="A7" s="12"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="151"/>
+      <c r="D7" s="151"/>
+      <c r="E7" s="151"/>
       <c r="F7" s="13" t="s">
         <v>86</v>
       </c>
@@ -2344,1755 +2401,1805 @@
       <c r="AB7" s="5"/>
     </row>
     <row r="8" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="45" t="s">
+      <c r="B8" s="163"/>
+      <c r="C8" s="163"/>
+      <c r="D8" s="163"/>
+      <c r="E8" s="163"/>
+      <c r="F8" s="163"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="163"/>
+      <c r="I8" s="163"/>
+      <c r="J8" s="166" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
-      <c r="V8" s="21"/>
-      <c r="W8" s="50"/>
-      <c r="X8" s="50"/>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="53" t="s">
+      <c r="K8" s="147"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
+      <c r="O8" s="147"/>
+      <c r="P8" s="147"/>
+      <c r="Q8" s="147"/>
+      <c r="R8" s="147"/>
+      <c r="S8" s="147"/>
+      <c r="T8" s="147"/>
+      <c r="U8" s="147"/>
+      <c r="V8" s="147"/>
+      <c r="W8" s="167"/>
+      <c r="X8" s="167"/>
+      <c r="Y8" s="167"/>
+      <c r="Z8" s="168"/>
+      <c r="AA8" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="AB8" s="50"/>
-      <c r="AC8" s="50"/>
-      <c r="AD8" s="20"/>
+      <c r="AB8" s="167"/>
+      <c r="AC8" s="167"/>
+      <c r="AD8" s="168"/>
     </row>
     <row r="9" spans="1:31" ht="17.25" customHeight="1">
-      <c r="A9" s="43"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="45" t="s">
+      <c r="A9" s="164"/>
+      <c r="B9" s="165"/>
+      <c r="C9" s="165"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="165"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="166" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="45" t="s">
+      <c r="K9" s="147"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="147"/>
+      <c r="N9" s="166" t="s">
         <v>10</v>
       </c>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="53" t="s">
+      <c r="O9" s="147"/>
+      <c r="P9" s="147"/>
+      <c r="Q9" s="147"/>
+      <c r="R9" s="168"/>
+      <c r="S9" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="54"/>
-      <c r="X9" s="57" t="s">
+      <c r="T9" s="157"/>
+      <c r="U9" s="157"/>
+      <c r="V9" s="157"/>
+      <c r="W9" s="157"/>
+      <c r="X9" s="158" t="s">
         <v>81</v>
       </c>
-      <c r="Y9" s="55"/>
-      <c r="Z9" s="56"/>
-      <c r="AA9" s="53" t="s">
+      <c r="Y9" s="159"/>
+      <c r="Z9" s="160"/>
+      <c r="AA9" s="156" t="s">
         <v>12</v>
       </c>
-      <c r="AB9" s="58"/>
-      <c r="AC9" s="54" t="s">
+      <c r="AB9" s="161"/>
+      <c r="AC9" s="157" t="s">
         <v>9</v>
       </c>
-      <c r="AD9" s="20"/>
+      <c r="AD9" s="168"/>
     </row>
     <row r="10" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="26" t="s">
+      <c r="C10" s="120"/>
+      <c r="D10" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="30" t="s">
+      <c r="E10" s="120"/>
+      <c r="F10" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="124" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="32"/>
-      <c r="I10" s="33" t="s">
+      <c r="H10" s="125"/>
+      <c r="I10" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="145">
         <v>9</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="145">
         <v>10</v>
       </c>
-      <c r="L10" s="59">
+      <c r="L10" s="152">
         <v>11</v>
       </c>
-      <c r="M10" s="40">
+      <c r="M10" s="169">
         <v>12</v>
       </c>
-      <c r="N10" s="35">
+      <c r="N10" s="139">
         <v>15</v>
       </c>
-      <c r="O10" s="35">
+      <c r="O10" s="139">
         <v>16</v>
       </c>
-      <c r="P10" s="36">
+      <c r="P10" s="170">
         <v>17</v>
       </c>
-      <c r="Q10" s="36">
+      <c r="Q10" s="170">
         <v>18</v>
       </c>
-      <c r="R10" s="61">
+      <c r="R10" s="171">
         <v>19</v>
       </c>
-      <c r="S10" s="35">
+      <c r="S10" s="139">
         <v>22</v>
       </c>
-      <c r="T10" s="35">
+      <c r="T10" s="139">
         <v>23</v>
       </c>
-      <c r="U10" s="36">
+      <c r="U10" s="170">
         <v>24</v>
       </c>
-      <c r="V10" s="36">
+      <c r="V10" s="170">
         <v>25</v>
       </c>
-      <c r="W10" s="51">
+      <c r="W10" s="154">
         <v>26</v>
       </c>
-      <c r="X10" s="35">
+      <c r="X10" s="139">
         <v>29</v>
       </c>
-      <c r="Y10" s="35">
+      <c r="Y10" s="139">
         <v>30</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="Z10" s="172">
         <v>31</v>
       </c>
-      <c r="AA10" s="35">
+      <c r="AA10" s="139">
         <v>1</v>
       </c>
-      <c r="AB10" s="35">
+      <c r="AB10" s="139">
         <v>2</v>
       </c>
-      <c r="AC10" s="35">
+      <c r="AC10" s="139">
         <v>5</v>
       </c>
-      <c r="AD10" s="35">
+      <c r="AD10" s="139">
         <v>6</v>
       </c>
-      <c r="AE10" s="38"/>
+      <c r="AE10" s="137"/>
     </row>
     <row r="11" spans="1:31" ht="18" customHeight="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="25"/>
+      <c r="A11" s="108"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="108"/>
       <c r="G11" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="25"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="60"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="52"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="23"/>
-      <c r="AB11" s="23"/>
-      <c r="AC11" s="23"/>
-      <c r="AD11" s="23"/>
-      <c r="AE11" s="39"/>
-    </row>
-    <row r="12" spans="1:31" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A12" s="69" t="s">
+      <c r="I11" s="108"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="140"/>
+      <c r="N11" s="140"/>
+      <c r="O11" s="140"/>
+      <c r="P11" s="140"/>
+      <c r="Q11" s="140"/>
+      <c r="R11" s="153"/>
+      <c r="S11" s="140"/>
+      <c r="T11" s="140"/>
+      <c r="U11" s="140"/>
+      <c r="V11" s="140"/>
+      <c r="W11" s="155"/>
+      <c r="X11" s="140"/>
+      <c r="Y11" s="140"/>
+      <c r="Z11" s="108"/>
+      <c r="AA11" s="140"/>
+      <c r="AB11" s="140"/>
+      <c r="AC11" s="140"/>
+      <c r="AD11" s="140"/>
+      <c r="AE11" s="138"/>
+    </row>
+    <row r="12" spans="1:31" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A12" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="75"/>
-      <c r="L12" s="75"/>
-      <c r="M12" s="75"/>
-      <c r="N12" s="75"/>
-      <c r="O12" s="75"/>
-      <c r="P12" s="75"/>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
-      <c r="T12" s="75"/>
-      <c r="U12" s="75"/>
-      <c r="V12" s="75"/>
-      <c r="W12" s="75"/>
-      <c r="X12" s="75"/>
-      <c r="Y12" s="75"/>
-      <c r="Z12" s="75"/>
-      <c r="AA12" s="75"/>
-      <c r="AB12" s="75"/>
-      <c r="AC12" s="75"/>
-      <c r="AD12" s="75"/>
-    </row>
-    <row r="13" spans="1:31" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A13" s="76"/>
-      <c r="B13" s="77" t="s">
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="132"/>
+      <c r="L12" s="132"/>
+      <c r="M12" s="132"/>
+      <c r="N12" s="132"/>
+      <c r="O12" s="132"/>
+      <c r="P12" s="132"/>
+      <c r="Q12" s="132"/>
+      <c r="R12" s="132"/>
+      <c r="S12" s="132"/>
+      <c r="T12" s="132"/>
+      <c r="U12" s="132"/>
+      <c r="V12" s="132"/>
+      <c r="W12" s="132"/>
+      <c r="X12" s="132"/>
+      <c r="Y12" s="132"/>
+      <c r="Z12" s="132"/>
+      <c r="AA12" s="132"/>
+      <c r="AB12" s="132"/>
+      <c r="AC12" s="132"/>
+      <c r="AD12" s="132"/>
+    </row>
+    <row r="13" spans="1:31" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A13" s="32"/>
+      <c r="B13" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="78" t="s">
+      <c r="C13" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82"/>
-      <c r="N13" s="82"/>
-      <c r="O13" s="82"/>
-      <c r="P13" s="82"/>
-      <c r="Q13" s="82"/>
-      <c r="R13" s="82"/>
-      <c r="S13" s="82"/>
-      <c r="T13" s="82"/>
-      <c r="U13" s="82"/>
-      <c r="V13" s="82"/>
-      <c r="W13" s="82"/>
-      <c r="X13" s="82"/>
-      <c r="Y13" s="82"/>
-      <c r="Z13" s="82"/>
-      <c r="AA13" s="82"/>
-      <c r="AB13" s="82"/>
-      <c r="AC13" s="82"/>
-      <c r="AD13" s="82"/>
-    </row>
-    <row r="14" spans="1:31" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A14" s="83"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="85" t="s">
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="98"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="113"/>
+      <c r="L13" s="113"/>
+      <c r="M13" s="113"/>
+      <c r="N13" s="113"/>
+      <c r="O13" s="113"/>
+      <c r="P13" s="113"/>
+      <c r="Q13" s="113"/>
+      <c r="R13" s="113"/>
+      <c r="S13" s="113"/>
+      <c r="T13" s="113"/>
+      <c r="U13" s="113"/>
+      <c r="V13" s="113"/>
+      <c r="W13" s="113"/>
+      <c r="X13" s="113"/>
+      <c r="Y13" s="113"/>
+      <c r="Z13" s="113"/>
+      <c r="AA13" s="113"/>
+      <c r="AB13" s="113"/>
+      <c r="AC13" s="113"/>
+      <c r="AD13" s="113"/>
+    </row>
+    <row r="14" spans="1:31" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A14" s="109"/>
+      <c r="B14" s="110"/>
+      <c r="C14" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="80"/>
-      <c r="E14" s="86" t="s">
+      <c r="D14" s="98"/>
+      <c r="E14" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="87" t="s">
+      <c r="F14" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="88">
+      <c r="G14" s="36">
         <v>46000</v>
       </c>
-      <c r="H14" s="88">
+      <c r="H14" s="36">
         <v>46000</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J14" s="89"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="90"/>
-      <c r="N14" s="90"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="90"/>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="90"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="90"/>
-      <c r="U14" s="90"/>
-      <c r="V14" s="90"/>
-      <c r="W14" s="90"/>
-      <c r="X14" s="90"/>
-      <c r="Y14" s="90"/>
-      <c r="Z14" s="90"/>
-      <c r="AA14" s="90"/>
-      <c r="AB14" s="90"/>
-      <c r="AC14" s="91"/>
-      <c r="AD14" s="91"/>
-    </row>
-    <row r="15" spans="1:31" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A15" s="83"/>
-      <c r="B15" s="84"/>
-      <c r="C15" s="85" t="s">
+      <c r="J14" s="37"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="38"/>
+      <c r="Z14" s="38"/>
+      <c r="AA14" s="38"/>
+      <c r="AB14" s="38"/>
+      <c r="AC14" s="39"/>
+      <c r="AD14" s="39"/>
+    </row>
+    <row r="15" spans="1:31" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A15" s="109"/>
+      <c r="B15" s="110"/>
+      <c r="C15" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="86" t="s">
+      <c r="D15" s="98"/>
+      <c r="E15" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="87" t="s">
+      <c r="F15" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="88">
+      <c r="G15" s="36">
         <v>46000</v>
       </c>
-      <c r="H15" s="88">
+      <c r="H15" s="36">
         <v>46000</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="J15" s="92"/>
-      <c r="K15" s="93"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="93"/>
-      <c r="O15" s="93"/>
-      <c r="P15" s="93"/>
-      <c r="Q15" s="93"/>
-      <c r="R15" s="93"/>
-      <c r="S15" s="93"/>
-      <c r="T15" s="93"/>
-      <c r="U15" s="93"/>
-      <c r="V15" s="93"/>
-      <c r="W15" s="93"/>
-      <c r="X15" s="93"/>
-      <c r="Y15" s="93"/>
-      <c r="Z15" s="93"/>
-      <c r="AA15" s="93"/>
-      <c r="AB15" s="93"/>
-      <c r="AC15" s="91"/>
-      <c r="AD15" s="91"/>
-    </row>
-    <row r="16" spans="1:31" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A16" s="76"/>
-      <c r="B16" s="77" t="s">
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="41"/>
+      <c r="S15" s="41"/>
+      <c r="T15" s="41"/>
+      <c r="U15" s="41"/>
+      <c r="V15" s="41"/>
+      <c r="W15" s="41"/>
+      <c r="X15" s="41"/>
+      <c r="Y15" s="41"/>
+      <c r="Z15" s="41"/>
+      <c r="AA15" s="41"/>
+      <c r="AB15" s="41"/>
+      <c r="AC15" s="39"/>
+      <c r="AD15" s="39"/>
+    </row>
+    <row r="16" spans="1:31" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A16" s="32"/>
+      <c r="B16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="94" t="s">
+      <c r="C16" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="82"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="82"/>
-      <c r="P16" s="82"/>
-      <c r="Q16" s="82"/>
-      <c r="R16" s="82"/>
-      <c r="S16" s="82"/>
-      <c r="T16" s="82"/>
-      <c r="U16" s="82"/>
-      <c r="V16" s="82"/>
-      <c r="W16" s="82"/>
-      <c r="X16" s="82"/>
-      <c r="Y16" s="82"/>
-      <c r="Z16" s="82"/>
-      <c r="AA16" s="82"/>
-      <c r="AB16" s="82"/>
-      <c r="AC16" s="82"/>
-      <c r="AD16" s="82"/>
-    </row>
-    <row r="17" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A17" s="83"/>
-      <c r="B17" s="84"/>
-      <c r="C17" s="85" t="s">
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113"/>
+      <c r="M16" s="113"/>
+      <c r="N16" s="113"/>
+      <c r="O16" s="113"/>
+      <c r="P16" s="113"/>
+      <c r="Q16" s="113"/>
+      <c r="R16" s="113"/>
+      <c r="S16" s="113"/>
+      <c r="T16" s="113"/>
+      <c r="U16" s="113"/>
+      <c r="V16" s="113"/>
+      <c r="W16" s="113"/>
+      <c r="X16" s="113"/>
+      <c r="Y16" s="113"/>
+      <c r="Z16" s="113"/>
+      <c r="AA16" s="113"/>
+      <c r="AB16" s="113"/>
+      <c r="AC16" s="113"/>
+      <c r="AD16" s="113"/>
+    </row>
+    <row r="17" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A17" s="109"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="80"/>
-      <c r="E17" s="86" t="s">
+      <c r="D17" s="98"/>
+      <c r="E17" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="95" t="s">
+      <c r="F17" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="G17" s="96" t="s">
+      <c r="G17" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="80"/>
+      <c r="H17" s="98"/>
       <c r="I17" s="15"/>
-      <c r="J17" s="90"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="90"/>
-      <c r="M17" s="90"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="93"/>
-      <c r="P17" s="93"/>
-      <c r="Q17" s="93"/>
-      <c r="R17" s="93"/>
-      <c r="S17" s="93"/>
-      <c r="T17" s="93"/>
-      <c r="U17" s="93"/>
-      <c r="V17" s="93"/>
-      <c r="W17" s="93"/>
-      <c r="X17" s="93"/>
-      <c r="Y17" s="93"/>
-      <c r="Z17" s="93"/>
-      <c r="AA17" s="93"/>
-      <c r="AB17" s="93"/>
-      <c r="AC17" s="91"/>
-      <c r="AD17" s="91"/>
-    </row>
-    <row r="18" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A18" s="69" t="s">
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="41"/>
+      <c r="W17" s="41"/>
+      <c r="X17" s="41"/>
+      <c r="Y17" s="41"/>
+      <c r="Z17" s="41"/>
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="41"/>
+      <c r="AC17" s="39"/>
+      <c r="AD17" s="39"/>
+    </row>
+    <row r="18" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A18" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="70"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="75"/>
-      <c r="L18" s="75"/>
-      <c r="M18" s="75"/>
-      <c r="N18" s="75"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="75"/>
-      <c r="Q18" s="75"/>
-      <c r="R18" s="75"/>
-      <c r="S18" s="75"/>
-      <c r="T18" s="75"/>
-      <c r="U18" s="75"/>
-      <c r="V18" s="75"/>
-      <c r="W18" s="75"/>
-      <c r="X18" s="75"/>
-      <c r="Y18" s="75"/>
-      <c r="Z18" s="75"/>
-      <c r="AA18" s="75"/>
-      <c r="AB18" s="75"/>
-      <c r="AC18" s="75"/>
-      <c r="AD18" s="75"/>
-    </row>
-    <row r="19" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A19" s="100"/>
-      <c r="B19" s="101" t="s">
+      <c r="B18" s="28"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="132"/>
+      <c r="L18" s="132"/>
+      <c r="M18" s="132"/>
+      <c r="N18" s="132"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="132"/>
+      <c r="Q18" s="132"/>
+      <c r="R18" s="132"/>
+      <c r="S18" s="132"/>
+      <c r="T18" s="132"/>
+      <c r="U18" s="132"/>
+      <c r="V18" s="132"/>
+      <c r="W18" s="132"/>
+      <c r="X18" s="132"/>
+      <c r="Y18" s="132"/>
+      <c r="Z18" s="132"/>
+      <c r="AA18" s="132"/>
+      <c r="AB18" s="132"/>
+      <c r="AC18" s="132"/>
+      <c r="AD18" s="132"/>
+    </row>
+    <row r="19" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A19" s="46"/>
+      <c r="B19" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="102" t="s">
+      <c r="C19" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="79"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="104"/>
-      <c r="K19" s="105"/>
-      <c r="L19" s="105"/>
-      <c r="M19" s="105"/>
-      <c r="N19" s="105"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="105"/>
-      <c r="Q19" s="105"/>
-      <c r="R19" s="105"/>
-      <c r="S19" s="105"/>
-      <c r="T19" s="105"/>
-      <c r="U19" s="105"/>
-      <c r="V19" s="105"/>
-      <c r="W19" s="105"/>
-      <c r="X19" s="105"/>
-      <c r="Y19" s="105"/>
-      <c r="Z19" s="105"/>
-      <c r="AA19" s="105"/>
-      <c r="AB19" s="105"/>
-      <c r="AC19" s="105"/>
-      <c r="AD19" s="105"/>
-    </row>
-    <row r="20" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A20" s="106"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="85" t="s">
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="134"/>
+      <c r="L19" s="134"/>
+      <c r="M19" s="134"/>
+      <c r="N19" s="134"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="134"/>
+      <c r="Q19" s="134"/>
+      <c r="R19" s="134"/>
+      <c r="S19" s="134"/>
+      <c r="T19" s="134"/>
+      <c r="U19" s="134"/>
+      <c r="V19" s="134"/>
+      <c r="W19" s="134"/>
+      <c r="X19" s="134"/>
+      <c r="Y19" s="134"/>
+      <c r="Z19" s="134"/>
+      <c r="AA19" s="134"/>
+      <c r="AB19" s="134"/>
+      <c r="AC19" s="134"/>
+      <c r="AD19" s="134"/>
+    </row>
+    <row r="20" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A20" s="111"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="114" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="80"/>
-      <c r="E20" s="86" t="s">
+      <c r="D20" s="98"/>
+      <c r="E20" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="87" t="s">
+      <c r="F20" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="88">
+      <c r="G20" s="36">
         <v>46000</v>
       </c>
-      <c r="H20" s="88">
-        <v>46000</v>
+      <c r="H20" s="36">
+        <v>46001</v>
       </c>
       <c r="I20" s="15"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="93"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
       <c r="Q20" s="15"/>
-      <c r="R20" s="93"/>
-      <c r="S20" s="93"/>
-      <c r="T20" s="93"/>
-      <c r="U20" s="93"/>
-      <c r="V20" s="93"/>
-      <c r="W20" s="93"/>
-      <c r="X20" s="93"/>
-      <c r="Y20" s="93"/>
-      <c r="Z20" s="93"/>
-      <c r="AA20" s="93"/>
-      <c r="AB20" s="93"/>
-      <c r="AC20" s="91"/>
-      <c r="AD20" s="91"/>
-    </row>
-    <row r="21" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A21" s="106"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="102" t="s">
+      <c r="R20" s="41"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="41"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="41"/>
+      <c r="W20" s="41"/>
+      <c r="X20" s="41"/>
+      <c r="Y20" s="41"/>
+      <c r="Z20" s="41"/>
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="41"/>
+      <c r="AC20" s="39"/>
+      <c r="AD20" s="39"/>
+    </row>
+    <row r="21" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A21" s="111"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="108"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="109"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
-      <c r="U21" s="109"/>
-      <c r="V21" s="109"/>
-      <c r="W21" s="109"/>
-      <c r="X21" s="109"/>
-      <c r="Y21" s="109"/>
-      <c r="Z21" s="109"/>
-      <c r="AA21" s="109"/>
-      <c r="AB21" s="109"/>
-      <c r="AC21" s="109"/>
-      <c r="AD21" s="109"/>
-    </row>
-    <row r="22" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A22" s="106"/>
-      <c r="B22" s="80"/>
-      <c r="C22" s="85" t="s">
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="135"/>
+      <c r="K21" s="136"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="136"/>
+      <c r="N21" s="136"/>
+      <c r="O21" s="136"/>
+      <c r="P21" s="136"/>
+      <c r="Q21" s="136"/>
+      <c r="R21" s="136"/>
+      <c r="S21" s="136"/>
+      <c r="T21" s="136"/>
+      <c r="U21" s="136"/>
+      <c r="V21" s="136"/>
+      <c r="W21" s="136"/>
+      <c r="X21" s="136"/>
+      <c r="Y21" s="136"/>
+      <c r="Z21" s="136"/>
+      <c r="AA21" s="136"/>
+      <c r="AB21" s="136"/>
+      <c r="AC21" s="136"/>
+      <c r="AD21" s="136"/>
+    </row>
+    <row r="22" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A22" s="111"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="80"/>
-      <c r="E22" s="86" t="s">
+      <c r="D22" s="98"/>
+      <c r="E22" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="110" t="s">
+      <c r="F22" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="88">
+      <c r="G22" s="36">
         <v>46000</v>
       </c>
-      <c r="H22" s="88">
+      <c r="H22" s="36">
         <v>46001</v>
       </c>
       <c r="I22" s="15"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="89"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
-      <c r="Q22" s="93"/>
-      <c r="R22" s="93"/>
-      <c r="S22" s="93"/>
-      <c r="T22" s="93"/>
-      <c r="U22" s="93"/>
-      <c r="V22" s="93"/>
-      <c r="W22" s="93"/>
-      <c r="X22" s="93"/>
-      <c r="Y22" s="93"/>
-      <c r="Z22" s="93"/>
-      <c r="AA22" s="93"/>
-      <c r="AB22" s="93"/>
-      <c r="AC22" s="91"/>
-      <c r="AD22" s="91"/>
-    </row>
-    <row r="23" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A23" s="106"/>
-      <c r="B23" s="80"/>
-      <c r="C23" s="85" t="s">
+      <c r="Q22" s="41"/>
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="41"/>
+      <c r="U22" s="41"/>
+      <c r="V22" s="41"/>
+      <c r="W22" s="41"/>
+      <c r="X22" s="41"/>
+      <c r="Y22" s="41"/>
+      <c r="Z22" s="41"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="41"/>
+      <c r="AC22" s="39"/>
+      <c r="AD22" s="39"/>
+    </row>
+    <row r="23" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A23" s="111"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="80"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="111" t="s">
+      <c r="D23" s="98"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="G23" s="88"/>
-      <c r="H23" s="88"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="15"/>
-      <c r="J23" s="112"/>
+      <c r="J23" s="51"/>
       <c r="K23" s="15"/>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
-      <c r="Q23" s="112"/>
-      <c r="R23" s="112"/>
-      <c r="S23" s="112"/>
-      <c r="T23" s="112"/>
-      <c r="U23" s="112"/>
-      <c r="V23" s="112"/>
-      <c r="W23" s="113"/>
-      <c r="X23" s="113"/>
-      <c r="Y23" s="113"/>
-      <c r="Z23" s="112"/>
-      <c r="AA23" s="112"/>
-      <c r="AB23" s="112"/>
-      <c r="AC23" s="114"/>
-      <c r="AD23" s="114"/>
-    </row>
-    <row r="24" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A24" s="106"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="85" t="s">
+      <c r="Q23" s="51"/>
+      <c r="R23" s="51"/>
+      <c r="S23" s="51"/>
+      <c r="T23" s="51"/>
+      <c r="U23" s="51"/>
+      <c r="V23" s="51"/>
+      <c r="W23" s="52"/>
+      <c r="X23" s="52"/>
+      <c r="Y23" s="52"/>
+      <c r="Z23" s="51"/>
+      <c r="AA23" s="51"/>
+      <c r="AB23" s="51"/>
+      <c r="AC23" s="53"/>
+      <c r="AD23" s="53"/>
+    </row>
+    <row r="24" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A24" s="111"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="114" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="80"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="115" t="s">
+      <c r="D24" s="98"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
       <c r="I24" s="15"/>
-      <c r="J24" s="112"/>
+      <c r="J24" s="51"/>
       <c r="K24" s="15"/>
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
-      <c r="Q24" s="112"/>
-      <c r="R24" s="112"/>
-      <c r="S24" s="112"/>
-      <c r="T24" s="112"/>
-      <c r="U24" s="112"/>
-      <c r="V24" s="112"/>
-      <c r="W24" s="113"/>
-      <c r="X24" s="113"/>
-      <c r="Y24" s="113"/>
-      <c r="Z24" s="112"/>
-      <c r="AA24" s="112"/>
-      <c r="AB24" s="112"/>
-      <c r="AC24" s="114"/>
-      <c r="AD24" s="114"/>
-    </row>
-    <row r="25" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A25" s="116" t="s">
+      <c r="Q24" s="51"/>
+      <c r="R24" s="51"/>
+      <c r="S24" s="51"/>
+      <c r="T24" s="51"/>
+      <c r="U24" s="51"/>
+      <c r="V24" s="51"/>
+      <c r="W24" s="52"/>
+      <c r="X24" s="52"/>
+      <c r="Y24" s="52"/>
+      <c r="Z24" s="51"/>
+      <c r="AA24" s="51"/>
+      <c r="AB24" s="51"/>
+      <c r="AC24" s="53"/>
+      <c r="AD24" s="53"/>
+    </row>
+    <row r="25" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A25" s="104" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="75"/>
-      <c r="L25" s="75"/>
-      <c r="M25" s="75"/>
-      <c r="N25" s="75"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
-      <c r="U25" s="75"/>
-      <c r="V25" s="75"/>
-      <c r="W25" s="75"/>
-      <c r="X25" s="75"/>
-      <c r="Y25" s="75"/>
-      <c r="Z25" s="75"/>
-      <c r="AA25" s="75"/>
-      <c r="AB25" s="75"/>
-      <c r="AC25" s="75"/>
-      <c r="AD25" s="75"/>
-    </row>
-    <row r="26" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A26" s="76"/>
-      <c r="B26" s="77" t="s">
+      <c r="B25" s="105"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="98"/>
+      <c r="J25" s="131"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="132"/>
+      <c r="M25" s="132"/>
+      <c r="N25" s="132"/>
+      <c r="O25" s="132"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="132"/>
+      <c r="R25" s="132"/>
+      <c r="S25" s="132"/>
+      <c r="T25" s="132"/>
+      <c r="U25" s="132"/>
+      <c r="V25" s="132"/>
+      <c r="W25" s="132"/>
+      <c r="X25" s="132"/>
+      <c r="Y25" s="132"/>
+      <c r="Z25" s="132"/>
+      <c r="AA25" s="132"/>
+      <c r="AB25" s="132"/>
+      <c r="AC25" s="132"/>
+      <c r="AD25" s="132"/>
+    </row>
+    <row r="26" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A26" s="32"/>
+      <c r="B26" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="78" t="s">
+      <c r="C26" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="82"/>
-      <c r="L26" s="82"/>
-      <c r="M26" s="82"/>
-      <c r="N26" s="82"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="82"/>
-      <c r="Q26" s="82"/>
-      <c r="R26" s="82"/>
-      <c r="S26" s="82"/>
-      <c r="T26" s="82"/>
-      <c r="U26" s="82"/>
-      <c r="V26" s="82"/>
-      <c r="W26" s="82"/>
-      <c r="X26" s="82"/>
-      <c r="Y26" s="82"/>
-      <c r="Z26" s="82"/>
-      <c r="AA26" s="82"/>
-      <c r="AB26" s="82"/>
-      <c r="AC26" s="82"/>
-      <c r="AD26" s="82"/>
-    </row>
-    <row r="27" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A27" s="117"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="118" t="s">
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="98"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="113"/>
+      <c r="L26" s="113"/>
+      <c r="M26" s="113"/>
+      <c r="N26" s="113"/>
+      <c r="O26" s="113"/>
+      <c r="P26" s="113"/>
+      <c r="Q26" s="113"/>
+      <c r="R26" s="113"/>
+      <c r="S26" s="113"/>
+      <c r="T26" s="113"/>
+      <c r="U26" s="113"/>
+      <c r="V26" s="113"/>
+      <c r="W26" s="113"/>
+      <c r="X26" s="113"/>
+      <c r="Y26" s="113"/>
+      <c r="Z26" s="113"/>
+      <c r="AA26" s="113"/>
+      <c r="AB26" s="113"/>
+      <c r="AC26" s="113"/>
+      <c r="AD26" s="113"/>
+    </row>
+    <row r="27" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A27" s="97"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="99" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="80"/>
-      <c r="E27" s="64" t="s">
+      <c r="D27" s="98"/>
+      <c r="E27" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="119" t="s">
+      <c r="F27" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="88">
+      <c r="G27" s="36">
         <v>46000</v>
       </c>
-      <c r="H27" s="88">
+      <c r="H27" s="36">
         <v>46001</v>
       </c>
-      <c r="I27" s="120"/>
-      <c r="J27" s="121"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="93"/>
-      <c r="O27" s="93"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="122"/>
-      <c r="R27" s="122"/>
-      <c r="S27" s="93"/>
-      <c r="T27" s="93"/>
-      <c r="U27" s="93"/>
-      <c r="V27" s="93"/>
-      <c r="W27" s="93"/>
-      <c r="X27" s="93"/>
-      <c r="Y27" s="93"/>
-      <c r="Z27" s="93"/>
-      <c r="AA27" s="93"/>
-      <c r="AB27" s="93"/>
-      <c r="AC27" s="91"/>
-      <c r="AD27" s="91"/>
-    </row>
-    <row r="28" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A28" s="117"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="118" t="s">
+      <c r="I27" s="56"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="58"/>
+      <c r="R27" s="58"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="41"/>
+      <c r="Z27" s="41"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
+      <c r="AC27" s="39"/>
+      <c r="AD27" s="39"/>
+    </row>
+    <row r="28" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A28" s="97"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="99" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="80"/>
-      <c r="E28" s="63" t="s">
+      <c r="D28" s="98"/>
+      <c r="E28" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="119" t="s">
+      <c r="F28" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="88"/>
-      <c r="H28" s="88"/>
-      <c r="I28" s="120"/>
-      <c r="J28" s="122"/>
-      <c r="K28" s="122"/>
-      <c r="L28" s="122"/>
-      <c r="M28" s="122"/>
-      <c r="N28" s="122"/>
-      <c r="O28" s="122"/>
-      <c r="P28" s="122"/>
-      <c r="Q28" s="122"/>
-      <c r="R28" s="122"/>
-      <c r="S28" s="122"/>
-      <c r="T28" s="122"/>
-      <c r="U28" s="122"/>
-      <c r="V28" s="93"/>
-      <c r="W28" s="93"/>
-      <c r="X28" s="93"/>
-      <c r="Y28" s="93"/>
-      <c r="Z28" s="93"/>
-      <c r="AA28" s="122"/>
-      <c r="AB28" s="122"/>
-      <c r="AC28" s="91"/>
-      <c r="AD28" s="91"/>
-    </row>
-    <row r="29" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A29" s="117"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="118" t="s">
+      <c r="G28" s="36">
+        <v>46001</v>
+      </c>
+      <c r="H28" s="36">
+        <v>46001</v>
+      </c>
+      <c r="I28" s="56"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="58"/>
+      <c r="S28" s="58"/>
+      <c r="T28" s="58"/>
+      <c r="U28" s="58"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="41"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="41"/>
+      <c r="AA28" s="58"/>
+      <c r="AB28" s="58"/>
+      <c r="AC28" s="39"/>
+      <c r="AD28" s="39"/>
+    </row>
+    <row r="29" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A29" s="97"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="80"/>
-      <c r="E29" s="64" t="s">
+      <c r="D29" s="98"/>
+      <c r="E29" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="119" t="s">
+      <c r="F29" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="120"/>
-      <c r="J29" s="122"/>
-      <c r="K29" s="122"/>
-      <c r="L29" s="122"/>
-      <c r="M29" s="122"/>
-      <c r="N29" s="122"/>
-      <c r="O29" s="122"/>
-      <c r="P29" s="122"/>
-      <c r="Q29" s="122"/>
-      <c r="R29" s="122"/>
-      <c r="S29" s="122"/>
-      <c r="T29" s="122"/>
-      <c r="U29" s="93"/>
-      <c r="V29" s="93"/>
-      <c r="W29" s="123"/>
-      <c r="X29" s="123"/>
-      <c r="Y29" s="123"/>
-      <c r="Z29" s="122"/>
-      <c r="AA29" s="122"/>
-      <c r="AB29" s="122"/>
-      <c r="AC29" s="91"/>
-      <c r="AD29" s="91"/>
-    </row>
-    <row r="30" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A30" s="117"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="118" t="s">
+      <c r="G29" s="36">
+        <v>46002</v>
+      </c>
+      <c r="H29" s="36">
+        <v>46002</v>
+      </c>
+      <c r="I29" s="56"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="58"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="58"/>
+      <c r="R29" s="58"/>
+      <c r="S29" s="58"/>
+      <c r="T29" s="58"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="59"/>
+      <c r="X29" s="59"/>
+      <c r="Y29" s="59"/>
+      <c r="Z29" s="58"/>
+      <c r="AA29" s="58"/>
+      <c r="AB29" s="58"/>
+      <c r="AC29" s="39"/>
+      <c r="AD29" s="39"/>
+    </row>
+    <row r="30" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A30" s="97"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="80"/>
-      <c r="E30" s="63" t="s">
+      <c r="D30" s="98"/>
+      <c r="E30" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="F30" s="119" t="s">
+      <c r="F30" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="G30" s="88"/>
-      <c r="H30" s="88"/>
-      <c r="I30" s="120"/>
-      <c r="J30" s="122"/>
-      <c r="K30" s="122"/>
-      <c r="L30" s="122"/>
-      <c r="M30" s="122"/>
-      <c r="N30" s="122"/>
-      <c r="O30" s="122"/>
-      <c r="P30" s="122"/>
-      <c r="Q30" s="122"/>
-      <c r="R30" s="122"/>
-      <c r="S30" s="122"/>
-      <c r="T30" s="122"/>
-      <c r="U30" s="122"/>
-      <c r="V30" s="122"/>
-      <c r="W30" s="123"/>
-      <c r="X30" s="123"/>
-      <c r="Y30" s="123"/>
-      <c r="Z30" s="122"/>
-      <c r="AA30" s="122"/>
-      <c r="AB30" s="122"/>
-      <c r="AC30" s="91"/>
-      <c r="AD30" s="91"/>
-    </row>
-    <row r="31" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A31" s="117"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="118" t="s">
+      <c r="G30" s="36">
+        <v>46003</v>
+      </c>
+      <c r="H30" s="36">
+        <v>46005</v>
+      </c>
+      <c r="I30" s="56"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="58"/>
+      <c r="R30" s="58"/>
+      <c r="S30" s="58"/>
+      <c r="T30" s="58"/>
+      <c r="U30" s="58"/>
+      <c r="V30" s="58"/>
+      <c r="W30" s="59"/>
+      <c r="X30" s="59"/>
+      <c r="Y30" s="59"/>
+      <c r="Z30" s="58"/>
+      <c r="AA30" s="58"/>
+      <c r="AB30" s="58"/>
+      <c r="AC30" s="39"/>
+      <c r="AD30" s="39"/>
+    </row>
+    <row r="31" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A31" s="97"/>
+      <c r="B31" s="98"/>
+      <c r="C31" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="80"/>
-      <c r="E31" s="65" t="s">
+      <c r="D31" s="98"/>
+      <c r="E31" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" s="36">
+        <v>46006</v>
+      </c>
+      <c r="H31" s="36">
+        <v>46008</v>
+      </c>
+      <c r="I31" s="56"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="58"/>
+      <c r="R31" s="58"/>
+      <c r="S31" s="58"/>
+      <c r="T31" s="58"/>
+      <c r="U31" s="58"/>
+      <c r="V31" s="58"/>
+      <c r="W31" s="59"/>
+      <c r="X31" s="59"/>
+      <c r="Y31" s="59"/>
+      <c r="Z31" s="58"/>
+      <c r="AA31" s="58"/>
+      <c r="AB31" s="58"/>
+      <c r="AC31" s="39"/>
+      <c r="AD31" s="39"/>
+    </row>
+    <row r="32" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A32" s="97"/>
+      <c r="B32" s="98"/>
+      <c r="C32" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="98"/>
+      <c r="E32" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="F32" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32" s="36">
+        <v>46009</v>
+      </c>
+      <c r="H32" s="36">
+        <v>46013</v>
+      </c>
+      <c r="I32" s="56"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="58"/>
+      <c r="Q32" s="58"/>
+      <c r="R32" s="58"/>
+      <c r="S32" s="58"/>
+      <c r="T32" s="58"/>
+      <c r="U32" s="58"/>
+      <c r="V32" s="58"/>
+      <c r="W32" s="59"/>
+      <c r="X32" s="59"/>
+      <c r="Y32" s="59"/>
+      <c r="Z32" s="58"/>
+      <c r="AA32" s="58"/>
+      <c r="AB32" s="58"/>
+      <c r="AC32" s="60"/>
+      <c r="AD32" s="60"/>
+    </row>
+    <row r="33" spans="1:30" s="23" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="A33" s="97"/>
+      <c r="B33" s="98"/>
+      <c r="C33" s="99" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="98"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="58"/>
+      <c r="N33" s="58"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="58"/>
+      <c r="Q33" s="58"/>
+      <c r="R33" s="58"/>
+      <c r="S33" s="58"/>
+      <c r="T33" s="58"/>
+      <c r="U33" s="58"/>
+      <c r="V33" s="58"/>
+      <c r="W33" s="59"/>
+      <c r="X33" s="59"/>
+      <c r="Y33" s="59"/>
+      <c r="Z33" s="58"/>
+      <c r="AA33" s="58"/>
+      <c r="AB33" s="58"/>
+      <c r="AC33" s="60"/>
+      <c r="AD33" s="60"/>
+    </row>
+    <row r="34" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A34" s="61"/>
+      <c r="B34" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="141"/>
+      <c r="K34" s="142"/>
+      <c r="L34" s="142"/>
+      <c r="M34" s="142"/>
+      <c r="N34" s="142"/>
+      <c r="O34" s="142"/>
+      <c r="P34" s="142"/>
+      <c r="Q34" s="142"/>
+      <c r="R34" s="142"/>
+      <c r="S34" s="142"/>
+      <c r="T34" s="142"/>
+      <c r="U34" s="142"/>
+      <c r="V34" s="142"/>
+      <c r="W34" s="142"/>
+      <c r="X34" s="142"/>
+      <c r="Y34" s="142"/>
+      <c r="Z34" s="142"/>
+      <c r="AA34" s="142"/>
+      <c r="AB34" s="142"/>
+      <c r="AC34" s="142"/>
+      <c r="AD34" s="142"/>
+    </row>
+    <row r="35" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A35" s="97"/>
+      <c r="B35" s="98"/>
+      <c r="C35" s="99" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="98"/>
+      <c r="E35" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="G35" s="36">
+        <v>46000</v>
+      </c>
+      <c r="H35" s="36">
+        <v>46001</v>
+      </c>
+      <c r="I35" s="56"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="58"/>
+      <c r="N35" s="58"/>
+      <c r="O35" s="58"/>
+      <c r="P35" s="58"/>
+      <c r="Q35" s="58"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="41"/>
+      <c r="U35" s="41"/>
+      <c r="V35" s="41"/>
+      <c r="W35" s="41"/>
+      <c r="X35" s="41"/>
+      <c r="Y35" s="41"/>
+      <c r="Z35" s="41"/>
+      <c r="AA35" s="41"/>
+      <c r="AB35" s="58"/>
+      <c r="AC35" s="66"/>
+      <c r="AD35" s="39"/>
+    </row>
+    <row r="36" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A36" s="97"/>
+      <c r="B36" s="98"/>
+      <c r="C36" s="99" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="98"/>
+      <c r="E36" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="F36" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="G36" s="36">
+        <v>46002</v>
+      </c>
+      <c r="H36" s="36">
+        <v>46008</v>
+      </c>
+      <c r="I36" s="56"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="58"/>
+      <c r="L36" s="58"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="58"/>
+      <c r="O36" s="58"/>
+      <c r="P36" s="58"/>
+      <c r="Q36" s="58"/>
+      <c r="R36" s="41"/>
+      <c r="S36" s="41"/>
+      <c r="T36" s="41"/>
+      <c r="U36" s="41"/>
+      <c r="V36" s="41"/>
+      <c r="W36" s="41"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="41"/>
+      <c r="Z36" s="41"/>
+      <c r="AA36" s="41"/>
+      <c r="AB36" s="58"/>
+      <c r="AC36" s="66"/>
+      <c r="AD36" s="39"/>
+    </row>
+    <row r="37" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A37" s="97"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="99" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="98"/>
+      <c r="E37" s="175" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="G37" s="36">
+        <v>46009</v>
+      </c>
+      <c r="H37" s="36">
+        <v>46010</v>
+      </c>
+      <c r="I37" s="56"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="58"/>
+      <c r="L37" s="58"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="58"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="41"/>
+      <c r="S37" s="41"/>
+      <c r="T37" s="41"/>
+      <c r="U37" s="41"/>
+      <c r="V37" s="41"/>
+      <c r="W37" s="41"/>
+      <c r="X37" s="41"/>
+      <c r="Y37" s="41"/>
+      <c r="Z37" s="41"/>
+      <c r="AA37" s="41"/>
+      <c r="AB37" s="41"/>
+      <c r="AC37" s="66"/>
+      <c r="AD37" s="39"/>
+    </row>
+    <row r="38" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A38" s="97"/>
+      <c r="B38" s="98"/>
+      <c r="C38" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="F31" s="119" t="s">
-        <v>74</v>
+      <c r="D38" s="98"/>
+      <c r="E38" s="175" t="s">
+        <v>109</v>
       </c>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="120"/>
-      <c r="J31" s="122"/>
-      <c r="K31" s="122"/>
-      <c r="L31" s="122"/>
-      <c r="M31" s="122"/>
-      <c r="N31" s="122"/>
-      <c r="O31" s="122"/>
-      <c r="P31" s="122"/>
-      <c r="Q31" s="122"/>
-      <c r="R31" s="122"/>
-      <c r="S31" s="122"/>
-      <c r="T31" s="122"/>
-      <c r="U31" s="122"/>
-      <c r="V31" s="122"/>
-      <c r="W31" s="123"/>
-      <c r="X31" s="123"/>
-      <c r="Y31" s="123"/>
-      <c r="Z31" s="122"/>
-      <c r="AA31" s="122"/>
-      <c r="AB31" s="122"/>
-      <c r="AC31" s="91"/>
-      <c r="AD31" s="91"/>
-    </row>
-    <row r="32" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A32" s="117"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="118" t="s">
-        <v>47</v>
+      <c r="F38" s="64" t="s">
+        <v>78</v>
       </c>
-      <c r="D32" s="80"/>
-      <c r="E32" s="63" t="s">
-        <v>96</v>
+      <c r="G38" s="36">
+        <v>46011</v>
       </c>
-      <c r="F32" s="119" t="s">
-        <v>74</v>
+      <c r="H38" s="36">
+        <v>46013</v>
       </c>
-      <c r="G32" s="88"/>
-      <c r="H32" s="88"/>
-      <c r="I32" s="120"/>
-      <c r="J32" s="122"/>
-      <c r="K32" s="122"/>
-      <c r="L32" s="122"/>
-      <c r="M32" s="122"/>
-      <c r="N32" s="122"/>
-      <c r="O32" s="122"/>
-      <c r="P32" s="122"/>
-      <c r="Q32" s="122"/>
-      <c r="R32" s="122"/>
-      <c r="S32" s="122"/>
-      <c r="T32" s="122"/>
-      <c r="U32" s="122"/>
-      <c r="V32" s="122"/>
-      <c r="W32" s="123"/>
-      <c r="X32" s="123"/>
-      <c r="Y32" s="123"/>
-      <c r="Z32" s="122"/>
-      <c r="AA32" s="122"/>
-      <c r="AB32" s="122"/>
-      <c r="AC32" s="124"/>
-      <c r="AD32" s="124"/>
-    </row>
-    <row r="33" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A33" s="117"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="118" t="s">
-        <v>48</v>
+      <c r="I38" s="56"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="58"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="41"/>
+      <c r="S38" s="41"/>
+      <c r="T38" s="41"/>
+      <c r="U38" s="41"/>
+      <c r="V38" s="41"/>
+      <c r="W38" s="41"/>
+      <c r="X38" s="41"/>
+      <c r="Y38" s="41"/>
+      <c r="Z38" s="41"/>
+      <c r="AA38" s="41"/>
+      <c r="AB38" s="41"/>
+      <c r="AC38" s="66"/>
+      <c r="AD38" s="39"/>
+    </row>
+    <row r="39" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A39" s="97"/>
+      <c r="B39" s="98"/>
+      <c r="C39" s="99" t="s">
+        <v>108</v>
       </c>
-      <c r="D33" s="80"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="119" t="s">
-        <v>74</v>
+      <c r="D39" s="98"/>
+      <c r="E39" s="175" t="s">
+        <v>106</v>
       </c>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="120"/>
-      <c r="J33" s="122"/>
-      <c r="K33" s="122"/>
-      <c r="L33" s="122"/>
-      <c r="M33" s="122"/>
-      <c r="N33" s="122"/>
-      <c r="O33" s="122"/>
-      <c r="P33" s="122"/>
-      <c r="Q33" s="122"/>
-      <c r="R33" s="122"/>
-      <c r="S33" s="122"/>
-      <c r="T33" s="122"/>
-      <c r="U33" s="122"/>
-      <c r="V33" s="122"/>
-      <c r="W33" s="123"/>
-      <c r="X33" s="123"/>
-      <c r="Y33" s="123"/>
-      <c r="Z33" s="122"/>
-      <c r="AA33" s="122"/>
-      <c r="AB33" s="122"/>
-      <c r="AC33" s="124"/>
-      <c r="AD33" s="124"/>
-    </row>
-    <row r="34" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A34" s="125"/>
-      <c r="B34" s="126" t="s">
-        <v>49</v>
+      <c r="F39" s="64" t="s">
+        <v>78</v>
       </c>
-      <c r="C34" s="78" t="s">
-        <v>88</v>
+      <c r="G39" s="36">
+        <v>46014</v>
       </c>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="80"/>
-      <c r="J34" s="127"/>
-      <c r="K34" s="128"/>
-      <c r="L34" s="128"/>
-      <c r="M34" s="128"/>
-      <c r="N34" s="128"/>
-      <c r="O34" s="128"/>
-      <c r="P34" s="128"/>
-      <c r="Q34" s="128"/>
-      <c r="R34" s="128"/>
-      <c r="S34" s="128"/>
-      <c r="T34" s="128"/>
-      <c r="U34" s="128"/>
-      <c r="V34" s="128"/>
-      <c r="W34" s="128"/>
-      <c r="X34" s="128"/>
-      <c r="Y34" s="128"/>
-      <c r="Z34" s="128"/>
-      <c r="AA34" s="128"/>
-      <c r="AB34" s="128"/>
-      <c r="AC34" s="128"/>
-      <c r="AD34" s="128"/>
-    </row>
-    <row r="35" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A35" s="117"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="118" t="s">
-        <v>50</v>
+      <c r="H39" s="36">
+        <v>46014</v>
       </c>
-      <c r="D35" s="80"/>
-      <c r="E35" s="129" t="s">
+      <c r="I39" s="56"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="58"/>
+      <c r="L39" s="58"/>
+      <c r="M39" s="58"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="58"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="41"/>
+      <c r="S39" s="41"/>
+      <c r="T39" s="41"/>
+      <c r="U39" s="41"/>
+      <c r="V39" s="41"/>
+      <c r="W39" s="41"/>
+      <c r="X39" s="41"/>
+      <c r="Y39" s="41"/>
+      <c r="Z39" s="41"/>
+      <c r="AA39" s="41"/>
+      <c r="AB39" s="41"/>
+      <c r="AC39" s="66"/>
+      <c r="AD39" s="39"/>
+    </row>
+    <row r="40" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A40" s="97"/>
+      <c r="B40" s="98"/>
+      <c r="C40" s="99" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="98"/>
+      <c r="E40" s="175"/>
+      <c r="F40" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="41"/>
+      <c r="S40" s="41"/>
+      <c r="T40" s="41"/>
+      <c r="U40" s="41"/>
+      <c r="V40" s="41"/>
+      <c r="W40" s="41"/>
+      <c r="X40" s="41"/>
+      <c r="Y40" s="41"/>
+      <c r="Z40" s="41"/>
+      <c r="AA40" s="41"/>
+      <c r="AB40" s="41"/>
+      <c r="AC40" s="66"/>
+      <c r="AD40" s="39"/>
+    </row>
+    <row r="41" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A41" s="67"/>
+      <c r="B41" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="106" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="105"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="98"/>
+      <c r="J41" s="141"/>
+      <c r="K41" s="142"/>
+      <c r="L41" s="142"/>
+      <c r="M41" s="142"/>
+      <c r="N41" s="142"/>
+      <c r="O41" s="142"/>
+      <c r="P41" s="142"/>
+      <c r="Q41" s="142"/>
+      <c r="R41" s="142"/>
+      <c r="S41" s="142"/>
+      <c r="T41" s="142"/>
+      <c r="U41" s="142"/>
+      <c r="V41" s="142"/>
+      <c r="W41" s="142"/>
+      <c r="X41" s="142"/>
+      <c r="Y41" s="142"/>
+      <c r="Z41" s="142"/>
+      <c r="AA41" s="142"/>
+      <c r="AB41" s="142"/>
+      <c r="AC41" s="142"/>
+      <c r="AD41" s="142"/>
+    </row>
+    <row r="42" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A42" s="69"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="127" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="98"/>
+      <c r="E42" s="70" t="s">
+        <v>92</v>
+      </c>
+      <c r="F42" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="G42" s="36">
+        <v>46000</v>
+      </c>
+      <c r="H42" s="36">
+        <v>46004</v>
+      </c>
+      <c r="I42" s="56"/>
+      <c r="J42" s="96"/>
+      <c r="K42" s="96"/>
+      <c r="L42" s="58"/>
+      <c r="M42" s="58"/>
+      <c r="N42" s="58"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="58"/>
+      <c r="Q42" s="58"/>
+      <c r="R42" s="41"/>
+      <c r="S42" s="58"/>
+      <c r="T42" s="58"/>
+      <c r="U42" s="58"/>
+      <c r="V42" s="58"/>
+      <c r="W42" s="59"/>
+      <c r="X42" s="59"/>
+      <c r="Y42" s="59"/>
+      <c r="Z42" s="58"/>
+      <c r="AA42" s="58"/>
+      <c r="AB42" s="58"/>
+      <c r="AC42" s="66"/>
+      <c r="AD42" s="39"/>
+    </row>
+    <row r="43" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A43" s="128"/>
+      <c r="B43" s="110"/>
+      <c r="C43" s="127" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="98"/>
+      <c r="E43" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="G43" s="36">
+        <v>46005</v>
+      </c>
+      <c r="H43" s="36">
+        <v>46008</v>
+      </c>
+      <c r="I43" s="56"/>
+      <c r="J43" s="58"/>
+      <c r="K43" s="58"/>
+      <c r="L43" s="58"/>
+      <c r="M43" s="58"/>
+      <c r="N43" s="41"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="41"/>
+      <c r="S43" s="41"/>
+      <c r="T43" s="41"/>
+      <c r="U43" s="41"/>
+      <c r="V43" s="41"/>
+      <c r="W43" s="41"/>
+      <c r="X43" s="41"/>
+      <c r="Y43" s="41"/>
+      <c r="Z43" s="41"/>
+      <c r="AA43" s="41"/>
+      <c r="AB43" s="41"/>
+      <c r="AC43" s="66"/>
+      <c r="AD43" s="39"/>
+    </row>
+    <row r="44" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A44" s="69"/>
+      <c r="B44" s="69"/>
+      <c r="C44" s="95" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="94"/>
+      <c r="E44" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="F44" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="G44" s="36">
+        <v>46009</v>
+      </c>
+      <c r="H44" s="36">
+        <v>46011</v>
+      </c>
+      <c r="I44" s="56"/>
+      <c r="J44" s="58"/>
+      <c r="K44" s="58"/>
+      <c r="L44" s="58"/>
+      <c r="M44" s="58"/>
+      <c r="N44" s="58"/>
+      <c r="O44" s="58"/>
+      <c r="P44" s="58"/>
+      <c r="Q44" s="58"/>
+      <c r="R44" s="58"/>
+      <c r="S44" s="58"/>
+      <c r="T44" s="58"/>
+      <c r="U44" s="58"/>
+      <c r="V44" s="58"/>
+      <c r="W44" s="59"/>
+      <c r="X44" s="59"/>
+      <c r="Y44" s="59"/>
+      <c r="Z44" s="58"/>
+      <c r="AA44" s="58"/>
+      <c r="AB44" s="58"/>
+      <c r="AC44" s="66"/>
+      <c r="AD44" s="39"/>
+    </row>
+    <row r="45" spans="1:30" s="23" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="A45" s="69"/>
+      <c r="B45" s="69"/>
+      <c r="C45" s="173" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" s="174"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="58"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="58"/>
+      <c r="O45" s="58"/>
+      <c r="P45" s="58"/>
+      <c r="Q45" s="58"/>
+      <c r="R45" s="58"/>
+      <c r="S45" s="58"/>
+      <c r="T45" s="58"/>
+      <c r="U45" s="58"/>
+      <c r="V45" s="58"/>
+      <c r="W45" s="59"/>
+      <c r="X45" s="59"/>
+      <c r="Y45" s="59"/>
+      <c r="Z45" s="58"/>
+      <c r="AA45" s="58"/>
+      <c r="AB45" s="58"/>
+      <c r="AC45" s="66"/>
+      <c r="AD45" s="39"/>
+    </row>
+    <row r="46" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A46" s="32"/>
+      <c r="B46" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="106" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="105"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="98"/>
+      <c r="J46" s="141"/>
+      <c r="K46" s="142"/>
+      <c r="L46" s="142"/>
+      <c r="M46" s="142"/>
+      <c r="N46" s="142"/>
+      <c r="O46" s="142"/>
+      <c r="P46" s="142"/>
+      <c r="Q46" s="142"/>
+      <c r="R46" s="142"/>
+      <c r="S46" s="142"/>
+      <c r="T46" s="142"/>
+      <c r="U46" s="142"/>
+      <c r="V46" s="142"/>
+      <c r="W46" s="142"/>
+      <c r="X46" s="142"/>
+      <c r="Y46" s="142"/>
+      <c r="Z46" s="142"/>
+      <c r="AA46" s="142"/>
+      <c r="AB46" s="142"/>
+      <c r="AC46" s="142"/>
+      <c r="AD46" s="142"/>
+    </row>
+    <row r="47" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A47" s="97"/>
+      <c r="B47" s="98"/>
+      <c r="C47" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" s="98"/>
+      <c r="E47" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="F47" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="G47" s="36">
+        <v>46000</v>
+      </c>
+      <c r="H47" s="36">
+        <v>46001</v>
+      </c>
+      <c r="I47" s="56"/>
+      <c r="J47" s="72"/>
+      <c r="K47" s="72"/>
+      <c r="L47" s="58"/>
+      <c r="M47" s="58"/>
+      <c r="N47" s="58"/>
+      <c r="O47" s="58"/>
+      <c r="P47" s="58"/>
+      <c r="Q47" s="58"/>
+      <c r="R47" s="58"/>
+      <c r="S47" s="41"/>
+      <c r="T47" s="58"/>
+      <c r="U47" s="58"/>
+      <c r="V47" s="58"/>
+      <c r="W47" s="58"/>
+      <c r="X47" s="58"/>
+      <c r="Y47" s="58"/>
+      <c r="Z47" s="58"/>
+      <c r="AA47" s="58"/>
+      <c r="AB47" s="58"/>
+      <c r="AC47" s="39"/>
+      <c r="AD47" s="39"/>
+    </row>
+    <row r="48" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A48" s="97"/>
+      <c r="B48" s="98"/>
+      <c r="C48" s="103" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" s="98"/>
+      <c r="E48" s="70" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" s="36">
+        <v>46002</v>
+      </c>
+      <c r="H48" s="36">
+        <v>46003</v>
+      </c>
+      <c r="I48" s="56"/>
+      <c r="J48" s="73"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="58"/>
+      <c r="M48" s="58"/>
+      <c r="N48" s="58"/>
+      <c r="O48" s="58"/>
+      <c r="P48" s="58"/>
+      <c r="Q48" s="58"/>
+      <c r="R48" s="58"/>
+      <c r="S48" s="58"/>
+      <c r="T48" s="58"/>
+      <c r="U48" s="58"/>
+      <c r="V48" s="58"/>
+      <c r="W48" s="58"/>
+      <c r="X48" s="58"/>
+      <c r="Y48" s="58"/>
+      <c r="Z48" s="58"/>
+      <c r="AA48" s="58"/>
+      <c r="AB48" s="58"/>
+      <c r="AC48" s="39"/>
+      <c r="AD48" s="39"/>
+    </row>
+    <row r="49" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A49" s="97"/>
+      <c r="B49" s="98"/>
+      <c r="C49" s="103" t="s">
+        <v>60</v>
+      </c>
+      <c r="D49" s="98"/>
+      <c r="E49" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="F49" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="G49" s="36">
+        <v>46004</v>
+      </c>
+      <c r="H49" s="36">
+        <v>46008</v>
+      </c>
+      <c r="I49" s="56"/>
+      <c r="J49" s="73"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
+      <c r="P49" s="58"/>
+      <c r="Q49" s="58"/>
+      <c r="R49" s="58"/>
+      <c r="S49" s="58"/>
+      <c r="T49" s="58"/>
+      <c r="U49" s="58"/>
+      <c r="V49" s="58"/>
+      <c r="W49" s="58"/>
+      <c r="X49" s="58"/>
+      <c r="Y49" s="58"/>
+      <c r="Z49" s="58"/>
+      <c r="AA49" s="58"/>
+      <c r="AB49" s="58"/>
+      <c r="AC49" s="39"/>
+      <c r="AD49" s="39"/>
+    </row>
+    <row r="50" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A50" s="97"/>
+      <c r="B50" s="98"/>
+      <c r="C50" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" s="98"/>
+      <c r="E50" s="70" t="s">
+        <v>99</v>
+      </c>
+      <c r="F50" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="G50" s="36">
+        <v>46009</v>
+      </c>
+      <c r="H50" s="36">
+        <v>46009</v>
+      </c>
+      <c r="I50" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="F35" s="130" t="s">
-        <v>78</v>
+      <c r="J50" s="73"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="58"/>
+      <c r="M50" s="58"/>
+      <c r="N50" s="58"/>
+      <c r="O50" s="58"/>
+      <c r="P50" s="58"/>
+      <c r="Q50" s="58"/>
+      <c r="R50" s="58"/>
+      <c r="S50" s="58"/>
+      <c r="T50" s="58"/>
+      <c r="U50" s="58"/>
+      <c r="V50" s="58"/>
+      <c r="W50" s="58"/>
+      <c r="X50" s="58"/>
+      <c r="Y50" s="58"/>
+      <c r="Z50" s="58"/>
+      <c r="AA50" s="58"/>
+      <c r="AB50" s="58"/>
+      <c r="AC50" s="39"/>
+      <c r="AD50" s="39"/>
+    </row>
+    <row r="51" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A51" s="97"/>
+      <c r="B51" s="98"/>
+      <c r="C51" s="103" t="s">
+        <v>114</v>
       </c>
-      <c r="G35" s="88">
-        <v>46000</v>
+      <c r="D51" s="98"/>
+      <c r="E51" s="70" t="s">
+        <v>100</v>
       </c>
-      <c r="H35" s="88">
-        <v>46001</v>
-      </c>
-      <c r="I35" s="120"/>
-      <c r="J35" s="131"/>
-      <c r="K35" s="122"/>
-      <c r="L35" s="122"/>
-      <c r="M35" s="122"/>
-      <c r="N35" s="122"/>
-      <c r="O35" s="122"/>
-      <c r="P35" s="122"/>
-      <c r="Q35" s="122"/>
-      <c r="R35" s="93"/>
-      <c r="S35" s="93"/>
-      <c r="T35" s="93"/>
-      <c r="U35" s="93"/>
-      <c r="V35" s="93"/>
-      <c r="W35" s="93"/>
-      <c r="X35" s="93"/>
-      <c r="Y35" s="93"/>
-      <c r="Z35" s="93"/>
-      <c r="AA35" s="93"/>
-      <c r="AB35" s="122"/>
-      <c r="AC35" s="132"/>
-      <c r="AD35" s="91"/>
-    </row>
-    <row r="36" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A36" s="117"/>
-      <c r="B36" s="80"/>
-      <c r="C36" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="80"/>
-      <c r="E36" s="133" t="s">
-        <v>103</v>
-      </c>
-      <c r="F36" s="130" t="s">
-        <v>78</v>
-      </c>
-      <c r="G36" s="88"/>
-      <c r="H36" s="88"/>
-      <c r="I36" s="120"/>
-      <c r="J36" s="122"/>
-      <c r="K36" s="122"/>
-      <c r="L36" s="122"/>
-      <c r="M36" s="122"/>
-      <c r="N36" s="122"/>
-      <c r="O36" s="122"/>
-      <c r="P36" s="93"/>
-      <c r="Q36" s="93"/>
-      <c r="R36" s="93"/>
-      <c r="S36" s="93"/>
-      <c r="T36" s="93"/>
-      <c r="U36" s="93"/>
-      <c r="V36" s="93"/>
-      <c r="W36" s="93"/>
-      <c r="X36" s="93"/>
-      <c r="Y36" s="93"/>
-      <c r="Z36" s="93"/>
-      <c r="AA36" s="93"/>
-      <c r="AB36" s="93"/>
-      <c r="AC36" s="132"/>
-      <c r="AD36" s="91"/>
-    </row>
-    <row r="37" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A37" s="117"/>
-      <c r="B37" s="80"/>
-      <c r="C37" s="118" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="80"/>
-      <c r="E37" s="134"/>
-      <c r="F37" s="130" t="s">
-        <v>78</v>
-      </c>
-      <c r="G37" s="88"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="120"/>
-      <c r="J37" s="122"/>
-      <c r="K37" s="122"/>
-      <c r="L37" s="122"/>
-      <c r="M37" s="122"/>
-      <c r="N37" s="122"/>
-      <c r="O37" s="122"/>
-      <c r="P37" s="93"/>
-      <c r="Q37" s="93"/>
-      <c r="R37" s="93"/>
-      <c r="S37" s="93"/>
-      <c r="T37" s="93"/>
-      <c r="U37" s="93"/>
-      <c r="V37" s="93"/>
-      <c r="W37" s="93"/>
-      <c r="X37" s="93"/>
-      <c r="Y37" s="93"/>
-      <c r="Z37" s="93"/>
-      <c r="AA37" s="93"/>
-      <c r="AB37" s="93"/>
-      <c r="AC37" s="132"/>
-      <c r="AD37" s="91"/>
-    </row>
-    <row r="38" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A38" s="135"/>
-      <c r="B38" s="136" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="78" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="80"/>
-      <c r="J38" s="127"/>
-      <c r="K38" s="128"/>
-      <c r="L38" s="128"/>
-      <c r="M38" s="128"/>
-      <c r="N38" s="128"/>
-      <c r="O38" s="128"/>
-      <c r="P38" s="128"/>
-      <c r="Q38" s="128"/>
-      <c r="R38" s="128"/>
-      <c r="S38" s="128"/>
-      <c r="T38" s="128"/>
-      <c r="U38" s="128"/>
-      <c r="V38" s="128"/>
-      <c r="W38" s="128"/>
-      <c r="X38" s="128"/>
-      <c r="Y38" s="128"/>
-      <c r="Z38" s="128"/>
-      <c r="AA38" s="128"/>
-      <c r="AB38" s="128"/>
-      <c r="AC38" s="128"/>
-      <c r="AD38" s="128"/>
-    </row>
-    <row r="39" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A39" s="137"/>
-      <c r="B39" s="137"/>
-      <c r="C39" s="138" t="s">
-        <v>54</v>
-      </c>
-      <c r="D39" s="80"/>
-      <c r="E39" s="139" t="s">
-        <v>92</v>
-      </c>
-      <c r="F39" s="95" t="s">
-        <v>72</v>
-      </c>
-      <c r="G39" s="88">
-        <v>46000</v>
-      </c>
-      <c r="H39" s="88">
-        <v>46005</v>
-      </c>
-      <c r="I39" s="120"/>
-      <c r="J39" s="122"/>
-      <c r="K39" s="122"/>
-      <c r="L39" s="122"/>
-      <c r="M39" s="122"/>
-      <c r="N39" s="122"/>
-      <c r="O39" s="93"/>
-      <c r="P39" s="122"/>
-      <c r="Q39" s="122"/>
-      <c r="R39" s="93"/>
-      <c r="S39" s="122"/>
-      <c r="T39" s="122"/>
-      <c r="U39" s="122"/>
-      <c r="V39" s="122"/>
-      <c r="W39" s="123"/>
-      <c r="X39" s="123"/>
-      <c r="Y39" s="123"/>
-      <c r="Z39" s="122"/>
-      <c r="AA39" s="122"/>
-      <c r="AB39" s="122"/>
-      <c r="AC39" s="132"/>
-      <c r="AD39" s="91"/>
-    </row>
-    <row r="40" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A40" s="140"/>
-      <c r="B40" s="84"/>
-      <c r="C40" s="138" t="s">
-        <v>55</v>
-      </c>
-      <c r="D40" s="80"/>
-      <c r="E40" s="129" t="s">
-        <v>105</v>
-      </c>
-      <c r="F40" s="95" t="s">
-        <v>72</v>
-      </c>
-      <c r="G40" s="88">
-        <v>46006</v>
-      </c>
-      <c r="H40" s="88">
-        <v>46008</v>
-      </c>
-      <c r="I40" s="120"/>
-      <c r="J40" s="122"/>
-      <c r="K40" s="122"/>
-      <c r="L40" s="122"/>
-      <c r="M40" s="122"/>
-      <c r="N40" s="93"/>
-      <c r="O40" s="93"/>
-      <c r="P40" s="93"/>
-      <c r="Q40" s="93"/>
-      <c r="R40" s="93"/>
-      <c r="S40" s="93"/>
-      <c r="T40" s="93"/>
-      <c r="U40" s="93"/>
-      <c r="V40" s="93"/>
-      <c r="W40" s="93"/>
-      <c r="X40" s="93"/>
-      <c r="Y40" s="93"/>
-      <c r="Z40" s="93"/>
-      <c r="AA40" s="93"/>
-      <c r="AB40" s="93"/>
-      <c r="AC40" s="132"/>
-      <c r="AD40" s="91"/>
-    </row>
-    <row r="41" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A41" s="137"/>
-      <c r="B41" s="137"/>
-      <c r="C41" s="138" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" s="80"/>
-      <c r="E41" s="139" t="s">
-        <v>106</v>
-      </c>
-      <c r="F41" s="95" t="s">
-        <v>72</v>
-      </c>
-      <c r="G41" s="88"/>
-      <c r="H41" s="88"/>
-      <c r="I41" s="120"/>
-      <c r="J41" s="122"/>
-      <c r="K41" s="122"/>
-      <c r="L41" s="122"/>
-      <c r="M41" s="122"/>
-      <c r="N41" s="122"/>
-      <c r="O41" s="122"/>
-      <c r="P41" s="122"/>
-      <c r="Q41" s="122"/>
-      <c r="R41" s="122"/>
-      <c r="S41" s="122"/>
-      <c r="T41" s="122"/>
-      <c r="U41" s="122"/>
-      <c r="V41" s="122"/>
-      <c r="W41" s="123"/>
-      <c r="X41" s="123"/>
-      <c r="Y41" s="123"/>
-      <c r="Z41" s="122"/>
-      <c r="AA41" s="122"/>
-      <c r="AB41" s="122"/>
-      <c r="AC41" s="132"/>
-      <c r="AD41" s="91"/>
-    </row>
-    <row r="42" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A42" s="76"/>
-      <c r="B42" s="77" t="s">
-        <v>57</v>
-      </c>
-      <c r="C42" s="78" t="s">
-        <v>90</v>
-      </c>
-      <c r="D42" s="79"/>
-      <c r="E42" s="79"/>
-      <c r="F42" s="79"/>
-      <c r="G42" s="79"/>
-      <c r="H42" s="79"/>
-      <c r="I42" s="80"/>
-      <c r="J42" s="127"/>
-      <c r="K42" s="128"/>
-      <c r="L42" s="128"/>
-      <c r="M42" s="128"/>
-      <c r="N42" s="128"/>
-      <c r="O42" s="128"/>
-      <c r="P42" s="128"/>
-      <c r="Q42" s="128"/>
-      <c r="R42" s="128"/>
-      <c r="S42" s="128"/>
-      <c r="T42" s="128"/>
-      <c r="U42" s="128"/>
-      <c r="V42" s="128"/>
-      <c r="W42" s="128"/>
-      <c r="X42" s="128"/>
-      <c r="Y42" s="128"/>
-      <c r="Z42" s="128"/>
-      <c r="AA42" s="128"/>
-      <c r="AB42" s="128"/>
-      <c r="AC42" s="128"/>
-      <c r="AD42" s="128"/>
-    </row>
-    <row r="43" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A43" s="117"/>
-      <c r="B43" s="80"/>
-      <c r="C43" s="141" t="s">
-        <v>58</v>
-      </c>
-      <c r="D43" s="80"/>
-      <c r="E43" s="129" t="s">
-        <v>97</v>
-      </c>
-      <c r="F43" s="142" t="s">
+      <c r="F51" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="G43" s="88">
-        <v>46000</v>
-      </c>
-      <c r="H43" s="88">
-        <v>46001</v>
-      </c>
-      <c r="I43" s="120"/>
-      <c r="J43" s="143"/>
-      <c r="K43" s="143"/>
-      <c r="L43" s="122"/>
-      <c r="M43" s="122"/>
-      <c r="N43" s="122"/>
-      <c r="O43" s="122"/>
-      <c r="P43" s="122"/>
-      <c r="Q43" s="122"/>
-      <c r="R43" s="122"/>
-      <c r="S43" s="93"/>
-      <c r="T43" s="122"/>
-      <c r="U43" s="122"/>
-      <c r="V43" s="122"/>
-      <c r="W43" s="122"/>
-      <c r="X43" s="122"/>
-      <c r="Y43" s="122"/>
-      <c r="Z43" s="122"/>
-      <c r="AA43" s="122"/>
-      <c r="AB43" s="122"/>
-      <c r="AC43" s="91"/>
-      <c r="AD43" s="91"/>
-    </row>
-    <row r="44" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A44" s="117"/>
-      <c r="B44" s="80"/>
-      <c r="C44" s="141" t="s">
-        <v>59</v>
-      </c>
-      <c r="D44" s="80"/>
-      <c r="E44" s="139" t="s">
-        <v>98</v>
-      </c>
-      <c r="F44" s="142" t="s">
-        <v>77</v>
-      </c>
-      <c r="G44" s="88">
-        <v>46002</v>
-      </c>
-      <c r="H44" s="88">
-        <v>46003</v>
-      </c>
-      <c r="I44" s="120"/>
-      <c r="J44" s="144"/>
-      <c r="K44" s="144"/>
-      <c r="L44" s="145"/>
-      <c r="M44" s="145"/>
-      <c r="N44" s="144"/>
-      <c r="O44" s="144"/>
-      <c r="P44" s="144"/>
-      <c r="Q44" s="144"/>
-      <c r="R44" s="122"/>
-      <c r="S44" s="122"/>
-      <c r="T44" s="122"/>
-      <c r="U44" s="122"/>
-      <c r="V44" s="122"/>
-      <c r="W44" s="122"/>
-      <c r="X44" s="122"/>
-      <c r="Y44" s="122"/>
-      <c r="Z44" s="122"/>
-      <c r="AA44" s="122"/>
-      <c r="AB44" s="122"/>
-      <c r="AC44" s="91"/>
-      <c r="AD44" s="91"/>
-    </row>
-    <row r="45" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A45" s="117"/>
-      <c r="B45" s="80"/>
-      <c r="C45" s="141" t="s">
-        <v>60</v>
-      </c>
-      <c r="D45" s="80"/>
-      <c r="E45" s="139" t="s">
-        <v>99</v>
-      </c>
-      <c r="F45" s="142" t="s">
-        <v>77</v>
-      </c>
-      <c r="G45" s="88">
-        <v>46006</v>
-      </c>
-      <c r="H45" s="88">
-        <v>46009</v>
-      </c>
-      <c r="I45" s="146" t="s">
-        <v>104</v>
-      </c>
-      <c r="J45" s="144"/>
-      <c r="K45" s="144"/>
-      <c r="L45" s="144"/>
-      <c r="M45" s="144"/>
-      <c r="N45" s="145"/>
-      <c r="O45" s="145"/>
-      <c r="P45" s="145"/>
-      <c r="Q45" s="145"/>
-      <c r="R45" s="143"/>
-      <c r="S45" s="122"/>
-      <c r="T45" s="122"/>
-      <c r="U45" s="122"/>
-      <c r="V45" s="122"/>
-      <c r="W45" s="122"/>
-      <c r="X45" s="122"/>
-      <c r="Y45" s="122"/>
-      <c r="Z45" s="122"/>
-      <c r="AA45" s="122"/>
-      <c r="AB45" s="122"/>
-      <c r="AC45" s="91"/>
-      <c r="AD45" s="91"/>
-    </row>
-    <row r="46" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A46" s="117"/>
-      <c r="B46" s="80"/>
-      <c r="C46" s="141" t="s">
-        <v>61</v>
-      </c>
-      <c r="D46" s="80"/>
-      <c r="E46" s="139" t="s">
-        <v>100</v>
-      </c>
-      <c r="F46" s="142" t="s">
-        <v>77</v>
-      </c>
-      <c r="G46" s="88">
+      <c r="G51" s="36">
         <v>46013</v>
       </c>
-      <c r="H46" s="88">
+      <c r="H51" s="36">
         <v>46015</v>
       </c>
-      <c r="I46" s="146"/>
-      <c r="J46" s="144"/>
-      <c r="K46" s="144"/>
-      <c r="L46" s="144"/>
-      <c r="M46" s="144"/>
-      <c r="N46" s="144"/>
-      <c r="O46" s="144"/>
-      <c r="P46" s="144"/>
-      <c r="Q46" s="144"/>
-      <c r="R46" s="122"/>
-      <c r="S46" s="143"/>
-      <c r="T46" s="143"/>
-      <c r="U46" s="143"/>
-      <c r="V46" s="122"/>
-      <c r="W46" s="123"/>
-      <c r="X46" s="123"/>
-      <c r="Y46" s="123"/>
-      <c r="Z46" s="122"/>
-      <c r="AA46" s="122"/>
-      <c r="AB46" s="123"/>
-      <c r="AC46" s="91"/>
-      <c r="AD46" s="91"/>
-    </row>
-    <row r="47" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A47" s="147" t="s">
+      <c r="I51" s="74"/>
+      <c r="J51" s="73"/>
+      <c r="K51" s="73"/>
+      <c r="L51" s="58"/>
+      <c r="M51" s="58"/>
+      <c r="N51" s="58"/>
+      <c r="O51" s="58"/>
+      <c r="P51" s="58"/>
+      <c r="Q51" s="58"/>
+      <c r="R51" s="58"/>
+      <c r="S51" s="58"/>
+      <c r="T51" s="58"/>
+      <c r="U51" s="58"/>
+      <c r="V51" s="58"/>
+      <c r="W51" s="59"/>
+      <c r="X51" s="59"/>
+      <c r="Y51" s="59"/>
+      <c r="Z51" s="58"/>
+      <c r="AA51" s="58"/>
+      <c r="AB51" s="59"/>
+      <c r="AC51" s="39"/>
+      <c r="AD51" s="39"/>
+    </row>
+    <row r="52" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A52" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="80"/>
-      <c r="C47" s="148" t="s">
+      <c r="B52" s="98"/>
+      <c r="C52" s="118" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="79"/>
-      <c r="E47" s="79"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="79"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="149"/>
-      <c r="K47" s="150"/>
-      <c r="L47" s="150"/>
-      <c r="M47" s="150"/>
-      <c r="N47" s="150"/>
-      <c r="O47" s="150"/>
-      <c r="P47" s="150"/>
-      <c r="Q47" s="150"/>
-      <c r="R47" s="150"/>
-      <c r="S47" s="150"/>
-      <c r="T47" s="150"/>
-      <c r="U47" s="150"/>
-      <c r="V47" s="150"/>
-      <c r="W47" s="150"/>
-      <c r="X47" s="150"/>
-      <c r="Y47" s="150"/>
-      <c r="Z47" s="150"/>
-      <c r="AA47" s="150"/>
-      <c r="AB47" s="150"/>
-      <c r="AC47" s="150"/>
-      <c r="AD47" s="150"/>
-    </row>
-    <row r="48" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A48" s="117"/>
-      <c r="B48" s="80"/>
-      <c r="C48" s="141" t="s">
-        <v>63</v>
-      </c>
-      <c r="D48" s="80"/>
-      <c r="E48" s="151"/>
-      <c r="F48" s="152"/>
-      <c r="G48" s="88">
-        <v>45371</v>
-      </c>
-      <c r="H48" s="88">
-        <v>45371</v>
-      </c>
-      <c r="I48" s="120"/>
-      <c r="J48" s="144"/>
-      <c r="K48" s="144"/>
-      <c r="L48" s="144"/>
-      <c r="M48" s="144"/>
-      <c r="N48" s="93"/>
-      <c r="O48" s="93"/>
-      <c r="P48" s="144"/>
-      <c r="Q48" s="144"/>
-      <c r="R48" s="93"/>
-      <c r="S48" s="93"/>
-      <c r="T48" s="93"/>
-      <c r="U48" s="93"/>
-      <c r="V48" s="93"/>
-      <c r="W48" s="93"/>
-      <c r="X48" s="93"/>
-      <c r="Y48" s="93"/>
-      <c r="Z48" s="93"/>
-      <c r="AA48" s="93"/>
-      <c r="AB48" s="93"/>
-      <c r="AC48" s="91"/>
-      <c r="AD48" s="91"/>
-    </row>
-    <row r="49" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A49" s="117"/>
-      <c r="B49" s="80"/>
-      <c r="C49" s="141" t="s">
-        <v>64</v>
-      </c>
-      <c r="D49" s="80"/>
-      <c r="E49" s="153"/>
-      <c r="F49" s="154"/>
-      <c r="G49" s="88">
-        <v>45372</v>
-      </c>
-      <c r="H49" s="88">
-        <v>45372</v>
-      </c>
-      <c r="I49" s="155"/>
-      <c r="J49" s="144"/>
-      <c r="K49" s="144"/>
-      <c r="L49" s="144"/>
-      <c r="M49" s="144"/>
-      <c r="N49" s="156"/>
-      <c r="O49" s="156"/>
-      <c r="P49" s="144"/>
-      <c r="Q49" s="144"/>
-      <c r="R49" s="156"/>
-      <c r="S49" s="156"/>
-      <c r="T49" s="156"/>
-      <c r="U49" s="156"/>
-      <c r="V49" s="156"/>
-      <c r="W49" s="156"/>
-      <c r="X49" s="156"/>
-      <c r="Y49" s="156"/>
-      <c r="Z49" s="156"/>
-      <c r="AA49" s="156"/>
-      <c r="AB49" s="156"/>
-      <c r="AC49" s="157"/>
-      <c r="AD49" s="157"/>
-    </row>
-    <row r="50" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A50" s="116" t="s">
-        <v>65</v>
-      </c>
-      <c r="B50" s="79"/>
-      <c r="C50" s="79"/>
-      <c r="D50" s="79"/>
-      <c r="E50" s="80"/>
-      <c r="F50" s="158"/>
-      <c r="G50" s="159"/>
-      <c r="H50" s="159"/>
-      <c r="I50" s="158"/>
-      <c r="J50" s="160"/>
-      <c r="K50" s="161"/>
-      <c r="L50" s="161"/>
-      <c r="M50" s="161"/>
-      <c r="N50" s="161"/>
-      <c r="O50" s="161"/>
-      <c r="P50" s="161"/>
-      <c r="Q50" s="161"/>
-      <c r="R50" s="161"/>
-      <c r="S50" s="161"/>
-      <c r="T50" s="161"/>
-      <c r="U50" s="161"/>
-      <c r="V50" s="161"/>
-      <c r="W50" s="161"/>
-      <c r="X50" s="161"/>
-      <c r="Y50" s="161"/>
-      <c r="Z50" s="161"/>
-      <c r="AA50" s="161"/>
-      <c r="AB50" s="161"/>
-      <c r="AC50" s="161"/>
-      <c r="AD50" s="161"/>
-    </row>
-    <row r="51" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A51" s="76"/>
-      <c r="B51" s="77" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="78" t="s">
-        <v>67</v>
-      </c>
-      <c r="D51" s="79"/>
-      <c r="E51" s="79"/>
-      <c r="F51" s="79"/>
-      <c r="G51" s="79"/>
-      <c r="H51" s="79"/>
-      <c r="I51" s="80"/>
-      <c r="J51" s="81"/>
-      <c r="K51" s="82"/>
-      <c r="L51" s="82"/>
-      <c r="M51" s="82"/>
-      <c r="N51" s="82"/>
-      <c r="O51" s="82"/>
-      <c r="P51" s="82"/>
-      <c r="Q51" s="82"/>
-      <c r="R51" s="82"/>
-      <c r="S51" s="82"/>
-      <c r="T51" s="82"/>
-      <c r="U51" s="82"/>
-      <c r="V51" s="82"/>
-      <c r="W51" s="82"/>
-      <c r="X51" s="82"/>
-      <c r="Y51" s="82"/>
-      <c r="Z51" s="82"/>
-      <c r="AA51" s="82"/>
-      <c r="AB51" s="82"/>
-      <c r="AC51" s="82"/>
-      <c r="AD51" s="82"/>
-    </row>
-    <row r="52" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A52" s="117"/>
-      <c r="B52" s="80"/>
-      <c r="C52" s="118" t="s">
-        <v>68</v>
-      </c>
-      <c r="D52" s="80"/>
-      <c r="E52" s="129"/>
-      <c r="F52" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="G52" s="88"/>
-      <c r="H52" s="88"/>
-      <c r="I52" s="120"/>
-      <c r="J52" s="144"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="105"/>
+      <c r="F52" s="105"/>
+      <c r="G52" s="105"/>
+      <c r="H52" s="105"/>
+      <c r="I52" s="98"/>
+      <c r="J52" s="143"/>
       <c r="K52" s="144"/>
       <c r="L52" s="144"/>
       <c r="M52" s="144"/>
@@ -4104,273 +4211,305 @@
       <c r="S52" s="144"/>
       <c r="T52" s="144"/>
       <c r="U52" s="144"/>
-      <c r="V52" s="162"/>
-      <c r="W52" s="163"/>
-      <c r="X52" s="163"/>
-      <c r="Y52" s="163"/>
-      <c r="Z52" s="162"/>
-      <c r="AA52" s="162"/>
-      <c r="AB52" s="162"/>
-      <c r="AC52" s="93"/>
-      <c r="AD52" s="93"/>
-    </row>
-    <row r="53" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A53" s="164"/>
-      <c r="B53" s="165"/>
-      <c r="C53" s="118" t="s">
+      <c r="V52" s="144"/>
+      <c r="W52" s="144"/>
+      <c r="X52" s="144"/>
+      <c r="Y52" s="144"/>
+      <c r="Z52" s="144"/>
+      <c r="AA52" s="144"/>
+      <c r="AB52" s="144"/>
+      <c r="AC52" s="144"/>
+      <c r="AD52" s="144"/>
+    </row>
+    <row r="53" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A53" s="97"/>
+      <c r="B53" s="98"/>
+      <c r="C53" s="103" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="98"/>
+      <c r="E53" s="75"/>
+      <c r="F53" s="76"/>
+      <c r="G53" s="36">
+        <v>45371</v>
+      </c>
+      <c r="H53" s="36">
+        <v>45371</v>
+      </c>
+      <c r="I53" s="56"/>
+      <c r="J53" s="73"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="73"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="41"/>
+      <c r="O53" s="41"/>
+      <c r="P53" s="73"/>
+      <c r="Q53" s="73"/>
+      <c r="R53" s="41"/>
+      <c r="S53" s="41"/>
+      <c r="T53" s="41"/>
+      <c r="U53" s="41"/>
+      <c r="V53" s="41"/>
+      <c r="W53" s="41"/>
+      <c r="X53" s="41"/>
+      <c r="Y53" s="41"/>
+      <c r="Z53" s="41"/>
+      <c r="AA53" s="41"/>
+      <c r="AB53" s="41"/>
+      <c r="AC53" s="39"/>
+      <c r="AD53" s="39"/>
+    </row>
+    <row r="54" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A54" s="97"/>
+      <c r="B54" s="98"/>
+      <c r="C54" s="103" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" s="98"/>
+      <c r="E54" s="77"/>
+      <c r="F54" s="78"/>
+      <c r="G54" s="36">
+        <v>45372</v>
+      </c>
+      <c r="H54" s="36">
+        <v>45372</v>
+      </c>
+      <c r="I54" s="79"/>
+      <c r="J54" s="73"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="73"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="80"/>
+      <c r="O54" s="80"/>
+      <c r="P54" s="73"/>
+      <c r="Q54" s="73"/>
+      <c r="R54" s="80"/>
+      <c r="S54" s="80"/>
+      <c r="T54" s="80"/>
+      <c r="U54" s="80"/>
+      <c r="V54" s="80"/>
+      <c r="W54" s="80"/>
+      <c r="X54" s="80"/>
+      <c r="Y54" s="80"/>
+      <c r="Z54" s="80"/>
+      <c r="AA54" s="80"/>
+      <c r="AB54" s="80"/>
+      <c r="AC54" s="81"/>
+      <c r="AD54" s="81"/>
+    </row>
+    <row r="55" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A55" s="104" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="105"/>
+      <c r="C55" s="105"/>
+      <c r="D55" s="105"/>
+      <c r="E55" s="98"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="83"/>
+      <c r="H55" s="83"/>
+      <c r="I55" s="82"/>
+      <c r="J55" s="129"/>
+      <c r="K55" s="130"/>
+      <c r="L55" s="130"/>
+      <c r="M55" s="130"/>
+      <c r="N55" s="130"/>
+      <c r="O55" s="130"/>
+      <c r="P55" s="130"/>
+      <c r="Q55" s="130"/>
+      <c r="R55" s="130"/>
+      <c r="S55" s="130"/>
+      <c r="T55" s="130"/>
+      <c r="U55" s="130"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="130"/>
+      <c r="X55" s="130"/>
+      <c r="Y55" s="130"/>
+      <c r="Z55" s="130"/>
+      <c r="AA55" s="130"/>
+      <c r="AB55" s="130"/>
+      <c r="AC55" s="130"/>
+      <c r="AD55" s="130"/>
+    </row>
+    <row r="56" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A56" s="32"/>
+      <c r="B56" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="106" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="105"/>
+      <c r="E56" s="105"/>
+      <c r="F56" s="105"/>
+      <c r="G56" s="105"/>
+      <c r="H56" s="105"/>
+      <c r="I56" s="98"/>
+      <c r="J56" s="112"/>
+      <c r="K56" s="113"/>
+      <c r="L56" s="113"/>
+      <c r="M56" s="113"/>
+      <c r="N56" s="113"/>
+      <c r="O56" s="113"/>
+      <c r="P56" s="113"/>
+      <c r="Q56" s="113"/>
+      <c r="R56" s="113"/>
+      <c r="S56" s="113"/>
+      <c r="T56" s="113"/>
+      <c r="U56" s="113"/>
+      <c r="V56" s="113"/>
+      <c r="W56" s="113"/>
+      <c r="X56" s="113"/>
+      <c r="Y56" s="113"/>
+      <c r="Z56" s="113"/>
+      <c r="AA56" s="113"/>
+      <c r="AB56" s="113"/>
+      <c r="AC56" s="113"/>
+      <c r="AD56" s="113"/>
+    </row>
+    <row r="57" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A57" s="97"/>
+      <c r="B57" s="98"/>
+      <c r="C57" s="99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" s="98"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="G57" s="36"/>
+      <c r="H57" s="36"/>
+      <c r="I57" s="56"/>
+      <c r="J57" s="73"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="73"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="73"/>
+      <c r="O57" s="73"/>
+      <c r="P57" s="73"/>
+      <c r="Q57" s="73"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="73"/>
+      <c r="T57" s="73"/>
+      <c r="U57" s="73"/>
+      <c r="V57" s="84"/>
+      <c r="W57" s="85"/>
+      <c r="X57" s="85"/>
+      <c r="Y57" s="85"/>
+      <c r="Z57" s="84"/>
+      <c r="AA57" s="84"/>
+      <c r="AB57" s="84"/>
+      <c r="AC57" s="41"/>
+      <c r="AD57" s="41"/>
+    </row>
+    <row r="58" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A58" s="86"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="D53" s="80"/>
-      <c r="E53" s="166"/>
-      <c r="F53" s="89" t="s">
+      <c r="D58" s="98"/>
+      <c r="E58" s="88"/>
+      <c r="F58" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="G53" s="88"/>
-      <c r="H53" s="88"/>
-      <c r="I53" s="120"/>
-      <c r="J53" s="144"/>
-      <c r="K53" s="144"/>
-      <c r="L53" s="144"/>
-      <c r="M53" s="144"/>
-      <c r="N53" s="93"/>
-      <c r="O53" s="93"/>
-      <c r="P53" s="93"/>
-      <c r="Q53" s="93"/>
-      <c r="R53" s="93"/>
-      <c r="S53" s="93"/>
-      <c r="T53" s="93"/>
-      <c r="U53" s="93"/>
-      <c r="V53" s="93"/>
-      <c r="W53" s="93"/>
-      <c r="X53" s="93"/>
-      <c r="Y53" s="93"/>
-      <c r="Z53" s="132"/>
-      <c r="AA53" s="167"/>
-      <c r="AB53" s="167"/>
-      <c r="AC53" s="167"/>
-      <c r="AD53" s="167"/>
-    </row>
-    <row r="54" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A54" s="117"/>
-      <c r="B54" s="80"/>
-      <c r="C54" s="168" t="s">
+      <c r="G58" s="36"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="56"/>
+      <c r="J58" s="73"/>
+      <c r="K58" s="73"/>
+      <c r="L58" s="73"/>
+      <c r="M58" s="73"/>
+      <c r="N58" s="41"/>
+      <c r="O58" s="41"/>
+      <c r="P58" s="41"/>
+      <c r="Q58" s="41"/>
+      <c r="R58" s="41"/>
+      <c r="S58" s="41"/>
+      <c r="T58" s="41"/>
+      <c r="U58" s="41"/>
+      <c r="V58" s="41"/>
+      <c r="W58" s="41"/>
+      <c r="X58" s="41"/>
+      <c r="Y58" s="41"/>
+      <c r="Z58" s="66"/>
+      <c r="AA58" s="89"/>
+      <c r="AB58" s="89"/>
+      <c r="AC58" s="89"/>
+      <c r="AD58" s="89"/>
+    </row>
+    <row r="59" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A59" s="97"/>
+      <c r="B59" s="98"/>
+      <c r="C59" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="169"/>
-      <c r="E54" s="170"/>
-      <c r="F54" s="89" t="s">
+      <c r="D59" s="101"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="G54" s="88"/>
-      <c r="H54" s="88"/>
-      <c r="I54" s="120"/>
-      <c r="J54" s="113"/>
-      <c r="K54" s="113"/>
-      <c r="L54" s="113"/>
-      <c r="M54" s="113"/>
-      <c r="N54" s="113"/>
-      <c r="O54" s="113"/>
-      <c r="P54" s="113"/>
-      <c r="Q54" s="113"/>
-      <c r="R54" s="113"/>
-      <c r="S54" s="113"/>
-      <c r="T54" s="113"/>
-      <c r="U54" s="113"/>
-      <c r="V54" s="113"/>
-      <c r="W54" s="171"/>
-      <c r="X54" s="171"/>
-      <c r="Y54" s="171"/>
-      <c r="Z54" s="162"/>
-      <c r="AA54" s="162"/>
-      <c r="AB54" s="162"/>
-      <c r="AC54" s="15"/>
-      <c r="AD54" s="93"/>
-    </row>
-    <row r="55" spans="1:30" s="65" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A55" s="117"/>
-      <c r="B55" s="80"/>
-      <c r="C55" s="168" t="s">
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="56"/>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
+      <c r="N59" s="52"/>
+      <c r="O59" s="52"/>
+      <c r="P59" s="52"/>
+      <c r="Q59" s="52"/>
+      <c r="R59" s="52"/>
+      <c r="S59" s="52"/>
+      <c r="T59" s="52"/>
+      <c r="U59" s="52"/>
+      <c r="V59" s="52"/>
+      <c r="W59" s="91"/>
+      <c r="X59" s="91"/>
+      <c r="Y59" s="91"/>
+      <c r="Z59" s="84"/>
+      <c r="AA59" s="84"/>
+      <c r="AB59" s="84"/>
+      <c r="AC59" s="15"/>
+      <c r="AD59" s="41"/>
+    </row>
+    <row r="60" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A60" s="97"/>
+      <c r="B60" s="98"/>
+      <c r="C60" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="D55" s="169"/>
-      <c r="E55" s="170"/>
-      <c r="F55" s="89" t="s">
+      <c r="D60" s="101"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="G55" s="88"/>
-      <c r="H55" s="88"/>
-      <c r="I55" s="120"/>
-      <c r="J55" s="93"/>
-      <c r="K55" s="93"/>
-      <c r="L55" s="93"/>
-      <c r="M55" s="93"/>
-      <c r="N55" s="93"/>
-      <c r="O55" s="93"/>
-      <c r="P55" s="93"/>
-      <c r="Q55" s="93"/>
-      <c r="R55" s="93"/>
-      <c r="S55" s="93"/>
-      <c r="T55" s="93"/>
-      <c r="U55" s="93"/>
-      <c r="V55" s="93"/>
-      <c r="W55" s="172"/>
-      <c r="X55" s="172"/>
-      <c r="Y55" s="172"/>
-      <c r="Z55" s="162"/>
-      <c r="AA55" s="162"/>
-      <c r="AB55" s="162"/>
-      <c r="AC55" s="173"/>
-      <c r="AD55" s="93"/>
-    </row>
-    <row r="56" spans="1:30" ht="16.5" customHeight="1">
-      <c r="A56" s="16"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="16"/>
-      <c r="O56" s="16"/>
-      <c r="P56" s="16"/>
-      <c r="Q56" s="16"/>
-      <c r="R56" s="16"/>
-      <c r="S56" s="16"/>
-      <c r="T56" s="16"/>
-      <c r="U56" s="16"/>
-      <c r="V56" s="16"/>
-      <c r="W56" s="16"/>
-      <c r="X56" s="16"/>
-      <c r="Y56" s="16"/>
-      <c r="Z56" s="16"/>
-      <c r="AA56" s="16"/>
-      <c r="AB56" s="16"/>
-    </row>
-    <row r="57" spans="1:30" ht="16.5" customHeight="1">
-      <c r="A57" s="16"/>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="16"/>
-      <c r="O57" s="16"/>
-      <c r="P57" s="16"/>
-      <c r="Q57" s="16"/>
-      <c r="R57" s="16"/>
-      <c r="S57" s="16"/>
-      <c r="T57" s="16"/>
-      <c r="U57" s="16"/>
-      <c r="V57" s="16"/>
-      <c r="W57" s="16"/>
-      <c r="X57" s="16"/>
-      <c r="Y57" s="16"/>
-      <c r="Z57" s="16"/>
-      <c r="AA57" s="16"/>
-      <c r="AB57" s="16"/>
-    </row>
-    <row r="58" spans="1:30" ht="16.5" customHeight="1">
-      <c r="A58" s="16"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="16"/>
-      <c r="O58" s="16"/>
-      <c r="P58" s="16"/>
-      <c r="Q58" s="16"/>
-      <c r="R58" s="16"/>
-      <c r="S58" s="16"/>
-      <c r="T58" s="16"/>
-      <c r="U58" s="16"/>
-      <c r="V58" s="16"/>
-      <c r="W58" s="16"/>
-      <c r="X58" s="16"/>
-      <c r="Y58" s="16"/>
-      <c r="Z58" s="16"/>
-      <c r="AA58" s="16"/>
-      <c r="AB58" s="16"/>
-    </row>
-    <row r="59" spans="1:30" ht="16.5" customHeight="1">
-      <c r="A59" s="16"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="16"/>
-      <c r="P59" s="16"/>
-      <c r="Q59" s="16"/>
-      <c r="R59" s="16"/>
-      <c r="S59" s="16"/>
-      <c r="T59" s="16"/>
-      <c r="U59" s="16"/>
-      <c r="V59" s="16"/>
-      <c r="W59" s="16"/>
-      <c r="X59" s="16"/>
-      <c r="Y59" s="16"/>
-      <c r="Z59" s="16"/>
-      <c r="AA59" s="16"/>
-      <c r="AB59" s="16"/>
-    </row>
-    <row r="60" spans="1:30" ht="16.5" customHeight="1">
-      <c r="A60" s="16"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="16"/>
-      <c r="O60" s="16"/>
-      <c r="P60" s="16"/>
-      <c r="Q60" s="16"/>
-      <c r="R60" s="16"/>
-      <c r="S60" s="16"/>
-      <c r="T60" s="16"/>
-      <c r="U60" s="16"/>
-      <c r="V60" s="16"/>
-      <c r="W60" s="16"/>
-      <c r="X60" s="16"/>
-      <c r="Y60" s="16"/>
-      <c r="Z60" s="16"/>
-      <c r="AA60" s="16"/>
-      <c r="AB60" s="16"/>
+      <c r="G60" s="36"/>
+      <c r="H60" s="36"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="41"/>
+      <c r="K60" s="41"/>
+      <c r="L60" s="41"/>
+      <c r="M60" s="41"/>
+      <c r="N60" s="41"/>
+      <c r="O60" s="41"/>
+      <c r="P60" s="41"/>
+      <c r="Q60" s="41"/>
+      <c r="R60" s="41"/>
+      <c r="S60" s="41"/>
+      <c r="T60" s="41"/>
+      <c r="U60" s="41"/>
+      <c r="V60" s="41"/>
+      <c r="W60" s="92"/>
+      <c r="X60" s="92"/>
+      <c r="Y60" s="92"/>
+      <c r="Z60" s="84"/>
+      <c r="AA60" s="84"/>
+      <c r="AB60" s="84"/>
+      <c r="AC60" s="93"/>
+      <c r="AD60" s="41"/>
     </row>
     <row r="61" spans="1:30" ht="16.5" customHeight="1">
       <c r="A61" s="16"/>
@@ -32762,6 +32901,25 @@
       <c r="G1007" s="18"/>
       <c r="H1007" s="18"/>
       <c r="I1007" s="5"/>
+      <c r="J1007" s="16"/>
+      <c r="K1007" s="16"/>
+      <c r="L1007" s="16"/>
+      <c r="M1007" s="16"/>
+      <c r="N1007" s="16"/>
+      <c r="O1007" s="16"/>
+      <c r="P1007" s="16"/>
+      <c r="Q1007" s="16"/>
+      <c r="R1007" s="16"/>
+      <c r="S1007" s="16"/>
+      <c r="T1007" s="16"/>
+      <c r="U1007" s="16"/>
+      <c r="V1007" s="16"/>
+      <c r="W1007" s="16"/>
+      <c r="X1007" s="16"/>
+      <c r="Y1007" s="16"/>
+      <c r="Z1007" s="16"/>
+      <c r="AA1007" s="16"/>
+      <c r="AB1007" s="16"/>
     </row>
     <row r="1008" spans="1:28" ht="16.5" customHeight="1">
       <c r="A1008" s="16"/>
@@ -32773,8 +32931,27 @@
       <c r="G1008" s="18"/>
       <c r="H1008" s="18"/>
       <c r="I1008" s="5"/>
-    </row>
-    <row r="1009" spans="1:9" ht="16.5" customHeight="1">
+      <c r="J1008" s="16"/>
+      <c r="K1008" s="16"/>
+      <c r="L1008" s="16"/>
+      <c r="M1008" s="16"/>
+      <c r="N1008" s="16"/>
+      <c r="O1008" s="16"/>
+      <c r="P1008" s="16"/>
+      <c r="Q1008" s="16"/>
+      <c r="R1008" s="16"/>
+      <c r="S1008" s="16"/>
+      <c r="T1008" s="16"/>
+      <c r="U1008" s="16"/>
+      <c r="V1008" s="16"/>
+      <c r="W1008" s="16"/>
+      <c r="X1008" s="16"/>
+      <c r="Y1008" s="16"/>
+      <c r="Z1008" s="16"/>
+      <c r="AA1008" s="16"/>
+      <c r="AB1008" s="16"/>
+    </row>
+    <row r="1009" spans="1:28" ht="16.5" customHeight="1">
       <c r="A1009" s="16"/>
       <c r="B1009" s="16"/>
       <c r="C1009" s="16"/>
@@ -32784,13 +32961,124 @@
       <c r="G1009" s="18"/>
       <c r="H1009" s="18"/>
       <c r="I1009" s="5"/>
+      <c r="J1009" s="16"/>
+      <c r="K1009" s="16"/>
+      <c r="L1009" s="16"/>
+      <c r="M1009" s="16"/>
+      <c r="N1009" s="16"/>
+      <c r="O1009" s="16"/>
+      <c r="P1009" s="16"/>
+      <c r="Q1009" s="16"/>
+      <c r="R1009" s="16"/>
+      <c r="S1009" s="16"/>
+      <c r="T1009" s="16"/>
+      <c r="U1009" s="16"/>
+      <c r="V1009" s="16"/>
+      <c r="W1009" s="16"/>
+      <c r="X1009" s="16"/>
+      <c r="Y1009" s="16"/>
+      <c r="Z1009" s="16"/>
+      <c r="AA1009" s="16"/>
+      <c r="AB1009" s="16"/>
+    </row>
+    <row r="1010" spans="1:28" ht="16.5" customHeight="1">
+      <c r="A1010" s="16"/>
+      <c r="B1010" s="16"/>
+      <c r="C1010" s="16"/>
+      <c r="D1010" s="16"/>
+      <c r="E1010" s="16"/>
+      <c r="F1010" s="17"/>
+      <c r="G1010" s="18"/>
+      <c r="H1010" s="18"/>
+      <c r="I1010" s="5"/>
+      <c r="J1010" s="16"/>
+      <c r="K1010" s="16"/>
+      <c r="L1010" s="16"/>
+      <c r="M1010" s="16"/>
+      <c r="N1010" s="16"/>
+      <c r="O1010" s="16"/>
+      <c r="P1010" s="16"/>
+      <c r="Q1010" s="16"/>
+      <c r="R1010" s="16"/>
+      <c r="S1010" s="16"/>
+      <c r="T1010" s="16"/>
+      <c r="U1010" s="16"/>
+      <c r="V1010" s="16"/>
+      <c r="W1010" s="16"/>
+      <c r="X1010" s="16"/>
+      <c r="Y1010" s="16"/>
+      <c r="Z1010" s="16"/>
+      <c r="AA1010" s="16"/>
+      <c r="AB1010" s="16"/>
+    </row>
+    <row r="1011" spans="1:28" ht="16.5" customHeight="1">
+      <c r="A1011" s="16"/>
+      <c r="B1011" s="16"/>
+      <c r="C1011" s="16"/>
+      <c r="D1011" s="16"/>
+      <c r="E1011" s="16"/>
+      <c r="F1011" s="17"/>
+      <c r="G1011" s="18"/>
+      <c r="H1011" s="18"/>
+      <c r="I1011" s="5"/>
+      <c r="J1011" s="16"/>
+      <c r="K1011" s="16"/>
+      <c r="L1011" s="16"/>
+      <c r="M1011" s="16"/>
+      <c r="N1011" s="16"/>
+      <c r="O1011" s="16"/>
+      <c r="P1011" s="16"/>
+      <c r="Q1011" s="16"/>
+      <c r="R1011" s="16"/>
+      <c r="S1011" s="16"/>
+      <c r="T1011" s="16"/>
+      <c r="U1011" s="16"/>
+      <c r="V1011" s="16"/>
+      <c r="W1011" s="16"/>
+      <c r="X1011" s="16"/>
+      <c r="Y1011" s="16"/>
+      <c r="Z1011" s="16"/>
+      <c r="AA1011" s="16"/>
+      <c r="AB1011" s="16"/>
+    </row>
+    <row r="1012" spans="1:28" ht="16.5" customHeight="1">
+      <c r="A1012" s="16"/>
+      <c r="B1012" s="16"/>
+      <c r="C1012" s="16"/>
+      <c r="D1012" s="16"/>
+      <c r="E1012" s="16"/>
+      <c r="F1012" s="17"/>
+      <c r="G1012" s="18"/>
+      <c r="H1012" s="18"/>
+      <c r="I1012" s="5"/>
+    </row>
+    <row r="1013" spans="1:28" ht="16.5" customHeight="1">
+      <c r="A1013" s="16"/>
+      <c r="B1013" s="16"/>
+      <c r="C1013" s="16"/>
+      <c r="D1013" s="16"/>
+      <c r="E1013" s="16"/>
+      <c r="F1013" s="17"/>
+      <c r="G1013" s="18"/>
+      <c r="H1013" s="18"/>
+      <c r="I1013" s="5"/>
+    </row>
+    <row r="1014" spans="1:28" ht="16.5" customHeight="1">
+      <c r="A1014" s="16"/>
+      <c r="B1014" s="16"/>
+      <c r="C1014" s="16"/>
+      <c r="D1014" s="16"/>
+      <c r="E1014" s="16"/>
+      <c r="F1014" s="17"/>
+      <c r="G1014" s="18"/>
+      <c r="H1014" s="18"/>
+      <c r="I1014" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="130">
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="W10:W11"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
+  <mergeCells count="138">
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
     <mergeCell ref="S9:W9"/>
     <mergeCell ref="X9:Z9"/>
     <mergeCell ref="AA9:AB9"/>
@@ -32809,6 +33097,19 @@
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="K10:K11"/>
     <mergeCell ref="L10:L11"/>
+    <mergeCell ref="AE10:AE11"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="AB10:AB11"/>
+    <mergeCell ref="AD10:AD11"/>
+    <mergeCell ref="AC10:AC11"/>
+    <mergeCell ref="J34:AD34"/>
+    <mergeCell ref="J41:AD41"/>
+    <mergeCell ref="J46:AD46"/>
+    <mergeCell ref="J52:AD52"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="W10:W11"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="M10:M11"/>
     <mergeCell ref="N10:N11"/>
     <mergeCell ref="O10:O11"/>
@@ -32820,17 +33121,8 @@
     <mergeCell ref="U10:U11"/>
     <mergeCell ref="V10:V11"/>
     <mergeCell ref="Z10:Z11"/>
-    <mergeCell ref="AE10:AE11"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="AB10:AB11"/>
-    <mergeCell ref="AD10:AD11"/>
-    <mergeCell ref="AC10:AC11"/>
-    <mergeCell ref="J34:AD34"/>
-    <mergeCell ref="J38:AD38"/>
-    <mergeCell ref="J42:AD42"/>
-    <mergeCell ref="J47:AD47"/>
-    <mergeCell ref="J50:AD50"/>
-    <mergeCell ref="J51:AD51"/>
+    <mergeCell ref="J55:AD55"/>
+    <mergeCell ref="J56:AD56"/>
     <mergeCell ref="J12:AD12"/>
     <mergeCell ref="J13:AD13"/>
     <mergeCell ref="J16:AD16"/>
@@ -32838,28 +33130,33 @@
     <mergeCell ref="J19:AD19"/>
     <mergeCell ref="J21:AD21"/>
     <mergeCell ref="J25:AD25"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:I42"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="C43:D43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C46:I46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C34:I34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:D35"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:I38"/>
-    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:I41"/>
     <mergeCell ref="C45:D45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:I47"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:I52"/>
     <mergeCell ref="B10:C11"/>
     <mergeCell ref="D10:E11"/>
     <mergeCell ref="F10:F11"/>
@@ -32878,8 +33175,16 @@
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="J26:AD26"/>
     <mergeCell ref="C13:I13"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C22:D22"/>
@@ -32894,29 +33199,21 @@
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C21:H21"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="J26:AD26"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:D60"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="A53:B53"/>
     <mergeCell ref="C53:D53"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="C54:D54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="C51:I51"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="C56:I56"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/자료/3. 프로젝트_WBS.xlsx
+++ b/자료/3. 프로젝트_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junse\Desktop\vscode\team-project\ONEPIC\자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE99B49-84D9-4440-A00D-D84D3232A080}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A1DA3F-269B-46EF-AE5D-2E7E6BD122BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1681,182 +1681,20 @@
     <xf numFmtId="0" fontId="13" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="15" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="21" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="21" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="23" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="23" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="16" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1891,11 +1729,68 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1909,14 +1804,119 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="15" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="23" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="23" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="16" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2163,12 +2163,12 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
       <c r="F1" s="11"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
@@ -2199,12 +2199,12 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
       <c r="F2" s="2" t="s">
         <v>72</v>
       </c>
@@ -2236,12 +2236,12 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="148" t="s">
+      <c r="B3" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
       <c r="F3" s="20" t="s">
         <v>77</v>
       </c>
@@ -2274,10 +2274,10 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="149"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
       <c r="F4" s="25" t="s">
         <v>74</v>
       </c>
@@ -2308,10 +2308,10 @@
       <c r="A5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="150"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="151"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
       <c r="F5" s="26" t="s">
         <v>78</v>
       </c>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="6" spans="1:31" ht="18.75" customHeight="1">
       <c r="A6" s="12"/>
-      <c r="B6" s="150"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="151"/>
-      <c r="E6" s="151"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="7" spans="1:31" ht="18.75" customHeight="1">
       <c r="A7" s="12"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="151"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
       <c r="F7" s="13" t="s">
         <v>86</v>
       </c>
@@ -2401,210 +2401,210 @@
       <c r="AB7" s="5"/>
     </row>
     <row r="8" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A8" s="162" t="s">
+      <c r="A8" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="163"/>
-      <c r="C8" s="163"/>
-      <c r="D8" s="163"/>
-      <c r="E8" s="163"/>
-      <c r="F8" s="163"/>
-      <c r="G8" s="163"/>
-      <c r="H8" s="163"/>
-      <c r="I8" s="163"/>
-      <c r="J8" s="166" t="s">
+      <c r="B8" s="109"/>
+      <c r="C8" s="109"/>
+      <c r="D8" s="109"/>
+      <c r="E8" s="109"/>
+      <c r="F8" s="109"/>
+      <c r="G8" s="109"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="112" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="147"/>
-      <c r="L8" s="147"/>
-      <c r="M8" s="147"/>
-      <c r="N8" s="147"/>
-      <c r="O8" s="147"/>
-      <c r="P8" s="147"/>
-      <c r="Q8" s="147"/>
-      <c r="R8" s="147"/>
-      <c r="S8" s="147"/>
-      <c r="T8" s="147"/>
-      <c r="U8" s="147"/>
-      <c r="V8" s="147"/>
-      <c r="W8" s="167"/>
-      <c r="X8" s="167"/>
-      <c r="Y8" s="167"/>
-      <c r="Z8" s="168"/>
-      <c r="AA8" s="156" t="s">
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="113"/>
+      <c r="N8" s="113"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="113"/>
+      <c r="S8" s="113"/>
+      <c r="T8" s="113"/>
+      <c r="U8" s="113"/>
+      <c r="V8" s="113"/>
+      <c r="W8" s="114"/>
+      <c r="X8" s="114"/>
+      <c r="Y8" s="114"/>
+      <c r="Z8" s="115"/>
+      <c r="AA8" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="AB8" s="167"/>
-      <c r="AC8" s="167"/>
-      <c r="AD8" s="168"/>
+      <c r="AB8" s="114"/>
+      <c r="AC8" s="114"/>
+      <c r="AD8" s="115"/>
     </row>
     <row r="9" spans="1:31" ht="17.25" customHeight="1">
-      <c r="A9" s="164"/>
-      <c r="B9" s="165"/>
-      <c r="C9" s="165"/>
-      <c r="D9" s="165"/>
-      <c r="E9" s="165"/>
-      <c r="F9" s="165"/>
-      <c r="G9" s="165"/>
-      <c r="H9" s="165"/>
-      <c r="I9" s="165"/>
-      <c r="J9" s="166" t="s">
+      <c r="A9" s="110"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="111"/>
+      <c r="J9" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="147"/>
-      <c r="L9" s="147"/>
-      <c r="M9" s="147"/>
-      <c r="N9" s="166" t="s">
+      <c r="K9" s="113"/>
+      <c r="L9" s="113"/>
+      <c r="M9" s="113"/>
+      <c r="N9" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="O9" s="147"/>
-      <c r="P9" s="147"/>
-      <c r="Q9" s="147"/>
-      <c r="R9" s="168"/>
-      <c r="S9" s="156" t="s">
+      <c r="O9" s="113"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="113"/>
+      <c r="R9" s="115"/>
+      <c r="S9" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="T9" s="157"/>
-      <c r="U9" s="157"/>
-      <c r="V9" s="157"/>
-      <c r="W9" s="157"/>
-      <c r="X9" s="158" t="s">
+      <c r="T9" s="103"/>
+      <c r="U9" s="103"/>
+      <c r="V9" s="103"/>
+      <c r="W9" s="103"/>
+      <c r="X9" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="Y9" s="159"/>
-      <c r="Z9" s="160"/>
-      <c r="AA9" s="156" t="s">
+      <c r="Y9" s="105"/>
+      <c r="Z9" s="106"/>
+      <c r="AA9" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="AB9" s="161"/>
-      <c r="AC9" s="157" t="s">
+      <c r="AB9" s="107"/>
+      <c r="AC9" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="AD9" s="168"/>
+      <c r="AD9" s="115"/>
     </row>
     <row r="10" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A10" s="107" t="s">
+      <c r="A10" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="119" t="s">
+      <c r="B10" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="120"/>
-      <c r="D10" s="119" t="s">
+      <c r="C10" s="158"/>
+      <c r="D10" s="157" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="120"/>
-      <c r="F10" s="123" t="s">
+      <c r="E10" s="158"/>
+      <c r="F10" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="124" t="s">
+      <c r="G10" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="125"/>
-      <c r="I10" s="126" t="s">
+      <c r="H10" s="163"/>
+      <c r="I10" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="145">
+      <c r="J10" s="121">
         <v>9</v>
       </c>
-      <c r="K10" s="145">
+      <c r="K10" s="121">
         <v>10</v>
       </c>
-      <c r="L10" s="152">
+      <c r="L10" s="123">
         <v>11</v>
       </c>
-      <c r="M10" s="169">
+      <c r="M10" s="134">
         <v>12</v>
       </c>
-      <c r="N10" s="139">
+      <c r="N10" s="127">
         <v>15</v>
       </c>
-      <c r="O10" s="139">
+      <c r="O10" s="127">
         <v>16</v>
       </c>
-      <c r="P10" s="170">
+      <c r="P10" s="135">
         <v>17</v>
       </c>
-      <c r="Q10" s="170">
+      <c r="Q10" s="135">
         <v>18</v>
       </c>
-      <c r="R10" s="171">
+      <c r="R10" s="136">
         <v>19</v>
       </c>
-      <c r="S10" s="139">
+      <c r="S10" s="127">
         <v>22</v>
       </c>
-      <c r="T10" s="139">
+      <c r="T10" s="127">
         <v>23</v>
       </c>
-      <c r="U10" s="170">
+      <c r="U10" s="135">
         <v>24</v>
       </c>
-      <c r="V10" s="170">
+      <c r="V10" s="135">
         <v>25</v>
       </c>
-      <c r="W10" s="154">
+      <c r="W10" s="132">
         <v>26</v>
       </c>
-      <c r="X10" s="139">
+      <c r="X10" s="127">
         <v>29</v>
       </c>
-      <c r="Y10" s="139">
+      <c r="Y10" s="127">
         <v>30</v>
       </c>
-      <c r="Z10" s="172">
+      <c r="Z10" s="137">
         <v>31</v>
       </c>
-      <c r="AA10" s="139">
+      <c r="AA10" s="127">
         <v>1</v>
       </c>
-      <c r="AB10" s="139">
+      <c r="AB10" s="127">
         <v>2</v>
       </c>
-      <c r="AC10" s="139">
+      <c r="AC10" s="127">
         <v>5</v>
       </c>
-      <c r="AD10" s="139">
+      <c r="AD10" s="127">
         <v>6</v>
       </c>
-      <c r="AE10" s="137"/>
+      <c r="AE10" s="125"/>
     </row>
     <row r="11" spans="1:31" ht="18" customHeight="1">
-      <c r="A11" s="108"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="108"/>
+      <c r="A11" s="138"/>
+      <c r="B11" s="159"/>
+      <c r="C11" s="160"/>
+      <c r="D11" s="159"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="138"/>
       <c r="G11" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="108"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="153"/>
-      <c r="M11" s="140"/>
-      <c r="N11" s="140"/>
-      <c r="O11" s="140"/>
-      <c r="P11" s="140"/>
-      <c r="Q11" s="140"/>
-      <c r="R11" s="153"/>
-      <c r="S11" s="140"/>
-      <c r="T11" s="140"/>
-      <c r="U11" s="140"/>
-      <c r="V11" s="140"/>
-      <c r="W11" s="155"/>
-      <c r="X11" s="140"/>
-      <c r="Y11" s="140"/>
-      <c r="Z11" s="108"/>
-      <c r="AA11" s="140"/>
-      <c r="AB11" s="140"/>
-      <c r="AC11" s="140"/>
-      <c r="AD11" s="140"/>
-      <c r="AE11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="122"/>
+      <c r="N11" s="122"/>
+      <c r="O11" s="122"/>
+      <c r="P11" s="122"/>
+      <c r="Q11" s="122"/>
+      <c r="R11" s="124"/>
+      <c r="S11" s="122"/>
+      <c r="T11" s="122"/>
+      <c r="U11" s="122"/>
+      <c r="V11" s="122"/>
+      <c r="W11" s="133"/>
+      <c r="X11" s="122"/>
+      <c r="Y11" s="122"/>
+      <c r="Z11" s="138"/>
+      <c r="AA11" s="122"/>
+      <c r="AB11" s="122"/>
+      <c r="AC11" s="122"/>
+      <c r="AD11" s="122"/>
+      <c r="AE11" s="126"/>
     </row>
     <row r="12" spans="1:31" s="23" customFormat="1" ht="16.5" customHeight="1">
       <c r="A12" s="27" t="s">
@@ -2618,71 +2618,71 @@
       <c r="G12" s="31"/>
       <c r="H12" s="31"/>
       <c r="I12" s="30"/>
-      <c r="J12" s="131"/>
-      <c r="K12" s="132"/>
-      <c r="L12" s="132"/>
-      <c r="M12" s="132"/>
-      <c r="N12" s="132"/>
-      <c r="O12" s="132"/>
-      <c r="P12" s="132"/>
-      <c r="Q12" s="132"/>
-      <c r="R12" s="132"/>
-      <c r="S12" s="132"/>
-      <c r="T12" s="132"/>
-      <c r="U12" s="132"/>
-      <c r="V12" s="132"/>
-      <c r="W12" s="132"/>
-      <c r="X12" s="132"/>
-      <c r="Y12" s="132"/>
-      <c r="Z12" s="132"/>
-      <c r="AA12" s="132"/>
-      <c r="AB12" s="132"/>
-      <c r="AC12" s="132"/>
-      <c r="AD12" s="132"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="144"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="144"/>
+      <c r="N12" s="144"/>
+      <c r="O12" s="144"/>
+      <c r="P12" s="144"/>
+      <c r="Q12" s="144"/>
+      <c r="R12" s="144"/>
+      <c r="S12" s="144"/>
+      <c r="T12" s="144"/>
+      <c r="U12" s="144"/>
+      <c r="V12" s="144"/>
+      <c r="W12" s="144"/>
+      <c r="X12" s="144"/>
+      <c r="Y12" s="144"/>
+      <c r="Z12" s="144"/>
+      <c r="AA12" s="144"/>
+      <c r="AB12" s="144"/>
+      <c r="AC12" s="144"/>
+      <c r="AD12" s="144"/>
     </row>
     <row r="13" spans="1:31" s="23" customFormat="1" ht="16.5" customHeight="1">
       <c r="A13" s="32"/>
       <c r="B13" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="106" t="s">
+      <c r="C13" s="152" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="105"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="112"/>
-      <c r="K13" s="113"/>
-      <c r="L13" s="113"/>
-      <c r="M13" s="113"/>
-      <c r="N13" s="113"/>
-      <c r="O13" s="113"/>
-      <c r="P13" s="113"/>
-      <c r="Q13" s="113"/>
-      <c r="R13" s="113"/>
-      <c r="S13" s="113"/>
-      <c r="T13" s="113"/>
-      <c r="U13" s="113"/>
-      <c r="V13" s="113"/>
-      <c r="W13" s="113"/>
-      <c r="X13" s="113"/>
-      <c r="Y13" s="113"/>
-      <c r="Z13" s="113"/>
-      <c r="AA13" s="113"/>
-      <c r="AB13" s="113"/>
-      <c r="AC13" s="113"/>
-      <c r="AD13" s="113"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="153"/>
+      <c r="H13" s="153"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="141"/>
+      <c r="K13" s="142"/>
+      <c r="L13" s="142"/>
+      <c r="M13" s="142"/>
+      <c r="N13" s="142"/>
+      <c r="O13" s="142"/>
+      <c r="P13" s="142"/>
+      <c r="Q13" s="142"/>
+      <c r="R13" s="142"/>
+      <c r="S13" s="142"/>
+      <c r="T13" s="142"/>
+      <c r="U13" s="142"/>
+      <c r="V13" s="142"/>
+      <c r="W13" s="142"/>
+      <c r="X13" s="142"/>
+      <c r="Y13" s="142"/>
+      <c r="Z13" s="142"/>
+      <c r="AA13" s="142"/>
+      <c r="AB13" s="142"/>
+      <c r="AC13" s="142"/>
+      <c r="AD13" s="142"/>
     </row>
     <row r="14" spans="1:31" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A14" s="109"/>
-      <c r="B14" s="110"/>
-      <c r="C14" s="114" t="s">
+      <c r="A14" s="166"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="168" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="98"/>
+      <c r="D14" s="99"/>
       <c r="E14" s="34" t="s">
         <v>75</v>
       </c>
@@ -2720,12 +2720,12 @@
       <c r="AD14" s="39"/>
     </row>
     <row r="15" spans="1:31" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A15" s="109"/>
-      <c r="B15" s="110"/>
-      <c r="C15" s="114" t="s">
+      <c r="A15" s="166"/>
+      <c r="B15" s="150"/>
+      <c r="C15" s="168" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="98"/>
+      <c r="D15" s="99"/>
       <c r="E15" s="34" t="s">
         <v>26</v>
       </c>
@@ -2768,54 +2768,54 @@
       <c r="B16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="105"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113"/>
-      <c r="O16" s="113"/>
-      <c r="P16" s="113"/>
-      <c r="Q16" s="113"/>
-      <c r="R16" s="113"/>
-      <c r="S16" s="113"/>
-      <c r="T16" s="113"/>
-      <c r="U16" s="113"/>
-      <c r="V16" s="113"/>
-      <c r="W16" s="113"/>
-      <c r="X16" s="113"/>
-      <c r="Y16" s="113"/>
-      <c r="Z16" s="113"/>
-      <c r="AA16" s="113"/>
-      <c r="AB16" s="113"/>
-      <c r="AC16" s="113"/>
-      <c r="AD16" s="113"/>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="153"/>
+      <c r="H16" s="153"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="142"/>
+      <c r="L16" s="142"/>
+      <c r="M16" s="142"/>
+      <c r="N16" s="142"/>
+      <c r="O16" s="142"/>
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="142"/>
+      <c r="S16" s="142"/>
+      <c r="T16" s="142"/>
+      <c r="U16" s="142"/>
+      <c r="V16" s="142"/>
+      <c r="W16" s="142"/>
+      <c r="X16" s="142"/>
+      <c r="Y16" s="142"/>
+      <c r="Z16" s="142"/>
+      <c r="AA16" s="142"/>
+      <c r="AB16" s="142"/>
+      <c r="AC16" s="142"/>
+      <c r="AD16" s="142"/>
     </row>
     <row r="17" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A17" s="109"/>
-      <c r="B17" s="110"/>
-      <c r="C17" s="114" t="s">
+      <c r="A17" s="166"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="168" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="98"/>
+      <c r="D17" s="99"/>
       <c r="E17" s="34" t="s">
         <v>85</v>
       </c>
       <c r="F17" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="G17" s="116" t="s">
+      <c r="G17" s="171" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="98"/>
+      <c r="H17" s="99"/>
       <c r="I17" s="15"/>
       <c r="J17" s="38"/>
       <c r="K17" s="38"/>
@@ -2851,71 +2851,71 @@
       <c r="G18" s="45"/>
       <c r="H18" s="45"/>
       <c r="I18" s="44"/>
-      <c r="J18" s="131"/>
-      <c r="K18" s="132"/>
-      <c r="L18" s="132"/>
-      <c r="M18" s="132"/>
-      <c r="N18" s="132"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="132"/>
-      <c r="Q18" s="132"/>
-      <c r="R18" s="132"/>
-      <c r="S18" s="132"/>
-      <c r="T18" s="132"/>
-      <c r="U18" s="132"/>
-      <c r="V18" s="132"/>
-      <c r="W18" s="132"/>
-      <c r="X18" s="132"/>
-      <c r="Y18" s="132"/>
-      <c r="Z18" s="132"/>
-      <c r="AA18" s="132"/>
-      <c r="AB18" s="132"/>
-      <c r="AC18" s="132"/>
-      <c r="AD18" s="132"/>
+      <c r="J18" s="143"/>
+      <c r="K18" s="144"/>
+      <c r="L18" s="144"/>
+      <c r="M18" s="144"/>
+      <c r="N18" s="144"/>
+      <c r="O18" s="144"/>
+      <c r="P18" s="144"/>
+      <c r="Q18" s="144"/>
+      <c r="R18" s="144"/>
+      <c r="S18" s="144"/>
+      <c r="T18" s="144"/>
+      <c r="U18" s="144"/>
+      <c r="V18" s="144"/>
+      <c r="W18" s="144"/>
+      <c r="X18" s="144"/>
+      <c r="Y18" s="144"/>
+      <c r="Z18" s="144"/>
+      <c r="AA18" s="144"/>
+      <c r="AB18" s="144"/>
+      <c r="AC18" s="144"/>
+      <c r="AD18" s="144"/>
     </row>
     <row r="19" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="172" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="105"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="153"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="153"/>
       <c r="I19" s="48"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="134"/>
-      <c r="L19" s="134"/>
-      <c r="M19" s="134"/>
-      <c r="N19" s="134"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="134"/>
-      <c r="Q19" s="134"/>
-      <c r="R19" s="134"/>
-      <c r="S19" s="134"/>
-      <c r="T19" s="134"/>
-      <c r="U19" s="134"/>
-      <c r="V19" s="134"/>
-      <c r="W19" s="134"/>
-      <c r="X19" s="134"/>
-      <c r="Y19" s="134"/>
-      <c r="Z19" s="134"/>
-      <c r="AA19" s="134"/>
-      <c r="AB19" s="134"/>
-      <c r="AC19" s="134"/>
-      <c r="AD19" s="134"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="146"/>
+      <c r="L19" s="146"/>
+      <c r="M19" s="146"/>
+      <c r="N19" s="146"/>
+      <c r="O19" s="146"/>
+      <c r="P19" s="146"/>
+      <c r="Q19" s="146"/>
+      <c r="R19" s="146"/>
+      <c r="S19" s="146"/>
+      <c r="T19" s="146"/>
+      <c r="U19" s="146"/>
+      <c r="V19" s="146"/>
+      <c r="W19" s="146"/>
+      <c r="X19" s="146"/>
+      <c r="Y19" s="146"/>
+      <c r="Z19" s="146"/>
+      <c r="AA19" s="146"/>
+      <c r="AB19" s="146"/>
+      <c r="AC19" s="146"/>
+      <c r="AD19" s="146"/>
     </row>
     <row r="20" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A20" s="111"/>
-      <c r="B20" s="98"/>
-      <c r="C20" s="114" t="s">
+      <c r="A20" s="167"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="168" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="98"/>
+      <c r="D20" s="99"/>
       <c r="E20" s="34" t="s">
         <v>84</v>
       </c>
@@ -2952,46 +2952,46 @@
       <c r="AD20" s="39"/>
     </row>
     <row r="21" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A21" s="111"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="117" t="s">
+      <c r="A21" s="167"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="172" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="105"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
+      <c r="D21" s="153"/>
+      <c r="E21" s="153"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="153"/>
+      <c r="H21" s="153"/>
       <c r="I21" s="48"/>
-      <c r="J21" s="135"/>
-      <c r="K21" s="136"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="136"/>
-      <c r="N21" s="136"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="136"/>
-      <c r="Q21" s="136"/>
-      <c r="R21" s="136"/>
-      <c r="S21" s="136"/>
-      <c r="T21" s="136"/>
-      <c r="U21" s="136"/>
-      <c r="V21" s="136"/>
-      <c r="W21" s="136"/>
-      <c r="X21" s="136"/>
-      <c r="Y21" s="136"/>
-      <c r="Z21" s="136"/>
-      <c r="AA21" s="136"/>
-      <c r="AB21" s="136"/>
-      <c r="AC21" s="136"/>
-      <c r="AD21" s="136"/>
+      <c r="J21" s="147"/>
+      <c r="K21" s="148"/>
+      <c r="L21" s="148"/>
+      <c r="M21" s="148"/>
+      <c r="N21" s="148"/>
+      <c r="O21" s="148"/>
+      <c r="P21" s="148"/>
+      <c r="Q21" s="148"/>
+      <c r="R21" s="148"/>
+      <c r="S21" s="148"/>
+      <c r="T21" s="148"/>
+      <c r="U21" s="148"/>
+      <c r="V21" s="148"/>
+      <c r="W21" s="148"/>
+      <c r="X21" s="148"/>
+      <c r="Y21" s="148"/>
+      <c r="Z21" s="148"/>
+      <c r="AA21" s="148"/>
+      <c r="AB21" s="148"/>
+      <c r="AC21" s="148"/>
+      <c r="AD21" s="148"/>
     </row>
     <row r="22" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A22" s="111"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="114" t="s">
+      <c r="A22" s="167"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="168" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="98"/>
+      <c r="D22" s="99"/>
       <c r="E22" s="34" t="s">
         <v>37</v>
       </c>
@@ -3028,12 +3028,12 @@
       <c r="AD22" s="39"/>
     </row>
     <row r="23" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A23" s="111"/>
-      <c r="B23" s="98"/>
-      <c r="C23" s="114" t="s">
+      <c r="A23" s="167"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="168" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="98"/>
+      <c r="D23" s="99"/>
       <c r="E23" s="34"/>
       <c r="F23" s="50" t="s">
         <v>4</v>
@@ -3064,12 +3064,12 @@
       <c r="AD23" s="53"/>
     </row>
     <row r="24" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A24" s="111"/>
-      <c r="B24" s="98"/>
-      <c r="C24" s="114" t="s">
+      <c r="A24" s="167"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="168" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="98"/>
+      <c r="D24" s="99"/>
       <c r="E24" s="34"/>
       <c r="F24" s="54" t="s">
         <v>4</v>
@@ -3100,82 +3100,82 @@
       <c r="AD24" s="53"/>
     </row>
     <row r="25" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A25" s="104" t="s">
+      <c r="A25" s="169" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="105"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="131"/>
-      <c r="K25" s="132"/>
-      <c r="L25" s="132"/>
-      <c r="M25" s="132"/>
-      <c r="N25" s="132"/>
-      <c r="O25" s="132"/>
-      <c r="P25" s="132"/>
-      <c r="Q25" s="132"/>
-      <c r="R25" s="132"/>
-      <c r="S25" s="132"/>
-      <c r="T25" s="132"/>
-      <c r="U25" s="132"/>
-      <c r="V25" s="132"/>
-      <c r="W25" s="132"/>
-      <c r="X25" s="132"/>
-      <c r="Y25" s="132"/>
-      <c r="Z25" s="132"/>
-      <c r="AA25" s="132"/>
-      <c r="AB25" s="132"/>
-      <c r="AC25" s="132"/>
-      <c r="AD25" s="132"/>
+      <c r="B25" s="153"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="99"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="144"/>
+      <c r="L25" s="144"/>
+      <c r="M25" s="144"/>
+      <c r="N25" s="144"/>
+      <c r="O25" s="144"/>
+      <c r="P25" s="144"/>
+      <c r="Q25" s="144"/>
+      <c r="R25" s="144"/>
+      <c r="S25" s="144"/>
+      <c r="T25" s="144"/>
+      <c r="U25" s="144"/>
+      <c r="V25" s="144"/>
+      <c r="W25" s="144"/>
+      <c r="X25" s="144"/>
+      <c r="Y25" s="144"/>
+      <c r="Z25" s="144"/>
+      <c r="AA25" s="144"/>
+      <c r="AB25" s="144"/>
+      <c r="AC25" s="144"/>
+      <c r="AD25" s="144"/>
     </row>
     <row r="26" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
       <c r="A26" s="32"/>
       <c r="B26" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="106" t="s">
+      <c r="C26" s="152" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="98"/>
-      <c r="J26" s="112"/>
-      <c r="K26" s="113"/>
-      <c r="L26" s="113"/>
-      <c r="M26" s="113"/>
-      <c r="N26" s="113"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="113"/>
-      <c r="Q26" s="113"/>
-      <c r="R26" s="113"/>
-      <c r="S26" s="113"/>
-      <c r="T26" s="113"/>
-      <c r="U26" s="113"/>
-      <c r="V26" s="113"/>
-      <c r="W26" s="113"/>
-      <c r="X26" s="113"/>
-      <c r="Y26" s="113"/>
-      <c r="Z26" s="113"/>
-      <c r="AA26" s="113"/>
-      <c r="AB26" s="113"/>
-      <c r="AC26" s="113"/>
-      <c r="AD26" s="113"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="153"/>
+      <c r="F26" s="153"/>
+      <c r="G26" s="153"/>
+      <c r="H26" s="153"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="142"/>
+      <c r="L26" s="142"/>
+      <c r="M26" s="142"/>
+      <c r="N26" s="142"/>
+      <c r="O26" s="142"/>
+      <c r="P26" s="142"/>
+      <c r="Q26" s="142"/>
+      <c r="R26" s="142"/>
+      <c r="S26" s="142"/>
+      <c r="T26" s="142"/>
+      <c r="U26" s="142"/>
+      <c r="V26" s="142"/>
+      <c r="W26" s="142"/>
+      <c r="X26" s="142"/>
+      <c r="Y26" s="142"/>
+      <c r="Z26" s="142"/>
+      <c r="AA26" s="142"/>
+      <c r="AB26" s="142"/>
+      <c r="AC26" s="142"/>
+      <c r="AD26" s="142"/>
     </row>
     <row r="27" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A27" s="97"/>
-      <c r="B27" s="98"/>
-      <c r="C27" s="99" t="s">
+      <c r="A27" s="100"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="98"/>
+      <c r="D27" s="99"/>
       <c r="E27" s="22" t="s">
         <v>94</v>
       </c>
@@ -3212,12 +3212,12 @@
       <c r="AD27" s="39"/>
     </row>
     <row r="28" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A28" s="97"/>
-      <c r="B28" s="98"/>
-      <c r="C28" s="99" t="s">
+      <c r="A28" s="100"/>
+      <c r="B28" s="99"/>
+      <c r="C28" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="98"/>
+      <c r="D28" s="99"/>
       <c r="E28" s="21" t="s">
         <v>93</v>
       </c>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="I28" s="56"/>
       <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
+      <c r="K28" s="57"/>
       <c r="L28" s="58"/>
       <c r="M28" s="58"/>
       <c r="N28" s="58"/>
@@ -3254,12 +3254,12 @@
       <c r="AD28" s="39"/>
     </row>
     <row r="29" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A29" s="97"/>
-      <c r="B29" s="98"/>
-      <c r="C29" s="99" t="s">
+      <c r="A29" s="100"/>
+      <c r="B29" s="99"/>
+      <c r="C29" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="98"/>
+      <c r="D29" s="99"/>
       <c r="E29" s="22" t="s">
         <v>95</v>
       </c>
@@ -3296,12 +3296,12 @@
       <c r="AD29" s="39"/>
     </row>
     <row r="30" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A30" s="97"/>
-      <c r="B30" s="98"/>
-      <c r="C30" s="99" t="s">
+      <c r="A30" s="100"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="98"/>
+      <c r="D30" s="99"/>
       <c r="E30" s="21" t="s">
         <v>101</v>
       </c>
@@ -3338,12 +3338,12 @@
       <c r="AD30" s="39"/>
     </row>
     <row r="31" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A31" s="97"/>
-      <c r="B31" s="98"/>
-      <c r="C31" s="99" t="s">
+      <c r="A31" s="100"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="98"/>
+      <c r="D31" s="99"/>
       <c r="E31" s="23" t="s">
         <v>113</v>
       </c>
@@ -3380,12 +3380,12 @@
       <c r="AD31" s="39"/>
     </row>
     <row r="32" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A32" s="97"/>
-      <c r="B32" s="98"/>
-      <c r="C32" s="99" t="s">
+      <c r="A32" s="100"/>
+      <c r="B32" s="99"/>
+      <c r="C32" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="98"/>
+      <c r="D32" s="99"/>
       <c r="E32" s="21" t="s">
         <v>96</v>
       </c>
@@ -3422,12 +3422,12 @@
       <c r="AD32" s="60"/>
     </row>
     <row r="33" spans="1:30" s="23" customFormat="1" ht="16.5" hidden="1" customHeight="1">
-      <c r="A33" s="97"/>
-      <c r="B33" s="98"/>
-      <c r="C33" s="99" t="s">
+      <c r="A33" s="100"/>
+      <c r="B33" s="99"/>
+      <c r="C33" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="98"/>
+      <c r="D33" s="99"/>
       <c r="E33" s="24"/>
       <c r="F33" s="55" t="s">
         <v>74</v>
@@ -3462,44 +3462,44 @@
       <c r="B34" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="106" t="s">
+      <c r="C34" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="141"/>
-      <c r="K34" s="142"/>
-      <c r="L34" s="142"/>
-      <c r="M34" s="142"/>
-      <c r="N34" s="142"/>
-      <c r="O34" s="142"/>
-      <c r="P34" s="142"/>
-      <c r="Q34" s="142"/>
-      <c r="R34" s="142"/>
-      <c r="S34" s="142"/>
-      <c r="T34" s="142"/>
-      <c r="U34" s="142"/>
-      <c r="V34" s="142"/>
-      <c r="W34" s="142"/>
-      <c r="X34" s="142"/>
-      <c r="Y34" s="142"/>
-      <c r="Z34" s="142"/>
-      <c r="AA34" s="142"/>
-      <c r="AB34" s="142"/>
-      <c r="AC34" s="142"/>
-      <c r="AD34" s="142"/>
+      <c r="D34" s="153"/>
+      <c r="E34" s="153"/>
+      <c r="F34" s="153"/>
+      <c r="G34" s="153"/>
+      <c r="H34" s="153"/>
+      <c r="I34" s="99"/>
+      <c r="J34" s="128"/>
+      <c r="K34" s="129"/>
+      <c r="L34" s="129"/>
+      <c r="M34" s="129"/>
+      <c r="N34" s="129"/>
+      <c r="O34" s="129"/>
+      <c r="P34" s="129"/>
+      <c r="Q34" s="129"/>
+      <c r="R34" s="129"/>
+      <c r="S34" s="129"/>
+      <c r="T34" s="129"/>
+      <c r="U34" s="129"/>
+      <c r="V34" s="129"/>
+      <c r="W34" s="129"/>
+      <c r="X34" s="129"/>
+      <c r="Y34" s="129"/>
+      <c r="Z34" s="129"/>
+      <c r="AA34" s="129"/>
+      <c r="AB34" s="129"/>
+      <c r="AC34" s="129"/>
+      <c r="AD34" s="129"/>
     </row>
     <row r="35" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A35" s="97"/>
-      <c r="B35" s="98"/>
-      <c r="C35" s="99" t="s">
+      <c r="A35" s="100"/>
+      <c r="B35" s="99"/>
+      <c r="C35" s="98" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="98"/>
+      <c r="D35" s="99"/>
       <c r="E35" s="63" t="s">
         <v>105</v>
       </c>
@@ -3536,12 +3536,12 @@
       <c r="AD35" s="39"/>
     </row>
     <row r="36" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A36" s="97"/>
-      <c r="B36" s="98"/>
-      <c r="C36" s="99" t="s">
+      <c r="A36" s="100"/>
+      <c r="B36" s="99"/>
+      <c r="C36" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="98"/>
+      <c r="D36" s="99"/>
       <c r="E36" s="63" t="s">
         <v>112</v>
       </c>
@@ -3578,13 +3578,13 @@
       <c r="AD36" s="39"/>
     </row>
     <row r="37" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A37" s="97"/>
-      <c r="B37" s="98"/>
-      <c r="C37" s="99" t="s">
+      <c r="A37" s="100"/>
+      <c r="B37" s="99"/>
+      <c r="C37" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="98"/>
-      <c r="E37" s="175" t="s">
+      <c r="D37" s="99"/>
+      <c r="E37" s="97" t="s">
         <v>110</v>
       </c>
       <c r="F37" s="64" t="s">
@@ -3620,13 +3620,13 @@
       <c r="AD37" s="39"/>
     </row>
     <row r="38" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A38" s="97"/>
-      <c r="B38" s="98"/>
-      <c r="C38" s="99" t="s">
+      <c r="A38" s="100"/>
+      <c r="B38" s="99"/>
+      <c r="C38" s="98" t="s">
         <v>107</v>
       </c>
-      <c r="D38" s="98"/>
-      <c r="E38" s="175" t="s">
+      <c r="D38" s="99"/>
+      <c r="E38" s="97" t="s">
         <v>109</v>
       </c>
       <c r="F38" s="64" t="s">
@@ -3662,13 +3662,13 @@
       <c r="AD38" s="39"/>
     </row>
     <row r="39" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A39" s="97"/>
-      <c r="B39" s="98"/>
-      <c r="C39" s="99" t="s">
+      <c r="A39" s="100"/>
+      <c r="B39" s="99"/>
+      <c r="C39" s="98" t="s">
         <v>108</v>
       </c>
-      <c r="D39" s="98"/>
-      <c r="E39" s="175" t="s">
+      <c r="D39" s="99"/>
+      <c r="E39" s="97" t="s">
         <v>106</v>
       </c>
       <c r="F39" s="64" t="s">
@@ -3704,13 +3704,13 @@
       <c r="AD39" s="39"/>
     </row>
     <row r="40" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A40" s="97"/>
-      <c r="B40" s="98"/>
-      <c r="C40" s="99" t="s">
+      <c r="A40" s="100"/>
+      <c r="B40" s="99"/>
+      <c r="C40" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="D40" s="98"/>
-      <c r="E40" s="175"/>
+      <c r="D40" s="99"/>
+      <c r="E40" s="97"/>
       <c r="F40" s="64" t="s">
         <v>78</v>
       </c>
@@ -3744,44 +3744,44 @@
       <c r="B41" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="106" t="s">
+      <c r="C41" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="105"/>
-      <c r="E41" s="105"/>
-      <c r="F41" s="105"/>
-      <c r="G41" s="105"/>
-      <c r="H41" s="105"/>
-      <c r="I41" s="98"/>
-      <c r="J41" s="141"/>
-      <c r="K41" s="142"/>
-      <c r="L41" s="142"/>
-      <c r="M41" s="142"/>
-      <c r="N41" s="142"/>
-      <c r="O41" s="142"/>
-      <c r="P41" s="142"/>
-      <c r="Q41" s="142"/>
-      <c r="R41" s="142"/>
-      <c r="S41" s="142"/>
-      <c r="T41" s="142"/>
-      <c r="U41" s="142"/>
-      <c r="V41" s="142"/>
-      <c r="W41" s="142"/>
-      <c r="X41" s="142"/>
-      <c r="Y41" s="142"/>
-      <c r="Z41" s="142"/>
-      <c r="AA41" s="142"/>
-      <c r="AB41" s="142"/>
-      <c r="AC41" s="142"/>
-      <c r="AD41" s="142"/>
+      <c r="D41" s="153"/>
+      <c r="E41" s="153"/>
+      <c r="F41" s="153"/>
+      <c r="G41" s="153"/>
+      <c r="H41" s="153"/>
+      <c r="I41" s="99"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="129"/>
+      <c r="L41" s="129"/>
+      <c r="M41" s="129"/>
+      <c r="N41" s="129"/>
+      <c r="O41" s="129"/>
+      <c r="P41" s="129"/>
+      <c r="Q41" s="129"/>
+      <c r="R41" s="129"/>
+      <c r="S41" s="129"/>
+      <c r="T41" s="129"/>
+      <c r="U41" s="129"/>
+      <c r="V41" s="129"/>
+      <c r="W41" s="129"/>
+      <c r="X41" s="129"/>
+      <c r="Y41" s="129"/>
+      <c r="Z41" s="129"/>
+      <c r="AA41" s="129"/>
+      <c r="AB41" s="129"/>
+      <c r="AC41" s="129"/>
+      <c r="AD41" s="129"/>
     </row>
     <row r="42" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
       <c r="A42" s="69"/>
       <c r="B42" s="69"/>
-      <c r="C42" s="127" t="s">
+      <c r="C42" s="151" t="s">
         <v>54</v>
       </c>
-      <c r="D42" s="98"/>
+      <c r="D42" s="99"/>
       <c r="E42" s="70" t="s">
         <v>92</v>
       </c>
@@ -3818,12 +3818,12 @@
       <c r="AD42" s="39"/>
     </row>
     <row r="43" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A43" s="128"/>
-      <c r="B43" s="110"/>
-      <c r="C43" s="127" t="s">
+      <c r="A43" s="149"/>
+      <c r="B43" s="150"/>
+      <c r="C43" s="151" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="98"/>
+      <c r="D43" s="99"/>
       <c r="E43" s="63" t="s">
         <v>103</v>
       </c>
@@ -3904,10 +3904,10 @@
     <row r="45" spans="1:30" s="23" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="A45" s="69"/>
       <c r="B45" s="69"/>
-      <c r="C45" s="173" t="s">
+      <c r="C45" s="154" t="s">
         <v>56</v>
       </c>
-      <c r="D45" s="174"/>
+      <c r="D45" s="155"/>
       <c r="E45" s="70"/>
       <c r="F45" s="42" t="s">
         <v>72</v>
@@ -3942,44 +3942,44 @@
       <c r="B46" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="106" t="s">
+      <c r="C46" s="152" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="105"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="105"/>
-      <c r="H46" s="105"/>
-      <c r="I46" s="98"/>
-      <c r="J46" s="141"/>
-      <c r="K46" s="142"/>
-      <c r="L46" s="142"/>
-      <c r="M46" s="142"/>
-      <c r="N46" s="142"/>
-      <c r="O46" s="142"/>
-      <c r="P46" s="142"/>
-      <c r="Q46" s="142"/>
-      <c r="R46" s="142"/>
-      <c r="S46" s="142"/>
-      <c r="T46" s="142"/>
-      <c r="U46" s="142"/>
-      <c r="V46" s="142"/>
-      <c r="W46" s="142"/>
-      <c r="X46" s="142"/>
-      <c r="Y46" s="142"/>
-      <c r="Z46" s="142"/>
-      <c r="AA46" s="142"/>
-      <c r="AB46" s="142"/>
-      <c r="AC46" s="142"/>
-      <c r="AD46" s="142"/>
+      <c r="D46" s="153"/>
+      <c r="E46" s="153"/>
+      <c r="F46" s="153"/>
+      <c r="G46" s="153"/>
+      <c r="H46" s="153"/>
+      <c r="I46" s="99"/>
+      <c r="J46" s="128"/>
+      <c r="K46" s="129"/>
+      <c r="L46" s="129"/>
+      <c r="M46" s="129"/>
+      <c r="N46" s="129"/>
+      <c r="O46" s="129"/>
+      <c r="P46" s="129"/>
+      <c r="Q46" s="129"/>
+      <c r="R46" s="129"/>
+      <c r="S46" s="129"/>
+      <c r="T46" s="129"/>
+      <c r="U46" s="129"/>
+      <c r="V46" s="129"/>
+      <c r="W46" s="129"/>
+      <c r="X46" s="129"/>
+      <c r="Y46" s="129"/>
+      <c r="Z46" s="129"/>
+      <c r="AA46" s="129"/>
+      <c r="AB46" s="129"/>
+      <c r="AC46" s="129"/>
+      <c r="AD46" s="129"/>
     </row>
     <row r="47" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A47" s="97"/>
-      <c r="B47" s="98"/>
-      <c r="C47" s="103" t="s">
+      <c r="A47" s="100"/>
+      <c r="B47" s="99"/>
+      <c r="C47" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="D47" s="98"/>
+      <c r="D47" s="99"/>
       <c r="E47" s="63" t="s">
         <v>97</v>
       </c>
@@ -4016,12 +4016,12 @@
       <c r="AD47" s="39"/>
     </row>
     <row r="48" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A48" s="97"/>
-      <c r="B48" s="98"/>
-      <c r="C48" s="103" t="s">
+      <c r="A48" s="100"/>
+      <c r="B48" s="99"/>
+      <c r="C48" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="D48" s="98"/>
+      <c r="D48" s="99"/>
       <c r="E48" s="70" t="s">
         <v>98</v>
       </c>
@@ -4058,12 +4058,12 @@
       <c r="AD48" s="39"/>
     </row>
     <row r="49" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A49" s="97"/>
-      <c r="B49" s="98"/>
-      <c r="C49" s="103" t="s">
+      <c r="A49" s="100"/>
+      <c r="B49" s="99"/>
+      <c r="C49" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="D49" s="98"/>
+      <c r="D49" s="99"/>
       <c r="E49" s="70" t="s">
         <v>115</v>
       </c>
@@ -4100,12 +4100,12 @@
       <c r="AD49" s="39"/>
     </row>
     <row r="50" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A50" s="97"/>
-      <c r="B50" s="98"/>
-      <c r="C50" s="103" t="s">
+      <c r="A50" s="100"/>
+      <c r="B50" s="99"/>
+      <c r="C50" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="D50" s="98"/>
+      <c r="D50" s="99"/>
       <c r="E50" s="70" t="s">
         <v>99</v>
       </c>
@@ -4144,12 +4144,12 @@
       <c r="AD50" s="39"/>
     </row>
     <row r="51" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A51" s="97"/>
-      <c r="B51" s="98"/>
-      <c r="C51" s="103" t="s">
+      <c r="A51" s="100"/>
+      <c r="B51" s="99"/>
+      <c r="C51" s="101" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="98"/>
+      <c r="D51" s="99"/>
       <c r="E51" s="70" t="s">
         <v>100</v>
       </c>
@@ -4186,48 +4186,48 @@
       <c r="AD51" s="39"/>
     </row>
     <row r="52" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A52" s="102" t="s">
+      <c r="A52" s="175" t="s">
         <v>62</v>
       </c>
-      <c r="B52" s="98"/>
-      <c r="C52" s="118" t="s">
+      <c r="B52" s="99"/>
+      <c r="C52" s="156" t="s">
         <v>91</v>
       </c>
-      <c r="D52" s="105"/>
-      <c r="E52" s="105"/>
-      <c r="F52" s="105"/>
-      <c r="G52" s="105"/>
-      <c r="H52" s="105"/>
-      <c r="I52" s="98"/>
-      <c r="J52" s="143"/>
-      <c r="K52" s="144"/>
-      <c r="L52" s="144"/>
-      <c r="M52" s="144"/>
-      <c r="N52" s="144"/>
-      <c r="O52" s="144"/>
-      <c r="P52" s="144"/>
-      <c r="Q52" s="144"/>
-      <c r="R52" s="144"/>
-      <c r="S52" s="144"/>
-      <c r="T52" s="144"/>
-      <c r="U52" s="144"/>
-      <c r="V52" s="144"/>
-      <c r="W52" s="144"/>
-      <c r="X52" s="144"/>
-      <c r="Y52" s="144"/>
-      <c r="Z52" s="144"/>
-      <c r="AA52" s="144"/>
-      <c r="AB52" s="144"/>
-      <c r="AC52" s="144"/>
-      <c r="AD52" s="144"/>
+      <c r="D52" s="153"/>
+      <c r="E52" s="153"/>
+      <c r="F52" s="153"/>
+      <c r="G52" s="153"/>
+      <c r="H52" s="153"/>
+      <c r="I52" s="99"/>
+      <c r="J52" s="130"/>
+      <c r="K52" s="131"/>
+      <c r="L52" s="131"/>
+      <c r="M52" s="131"/>
+      <c r="N52" s="131"/>
+      <c r="O52" s="131"/>
+      <c r="P52" s="131"/>
+      <c r="Q52" s="131"/>
+      <c r="R52" s="131"/>
+      <c r="S52" s="131"/>
+      <c r="T52" s="131"/>
+      <c r="U52" s="131"/>
+      <c r="V52" s="131"/>
+      <c r="W52" s="131"/>
+      <c r="X52" s="131"/>
+      <c r="Y52" s="131"/>
+      <c r="Z52" s="131"/>
+      <c r="AA52" s="131"/>
+      <c r="AB52" s="131"/>
+      <c r="AC52" s="131"/>
+      <c r="AD52" s="131"/>
     </row>
     <row r="53" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A53" s="97"/>
-      <c r="B53" s="98"/>
-      <c r="C53" s="103" t="s">
+      <c r="A53" s="100"/>
+      <c r="B53" s="99"/>
+      <c r="C53" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="98"/>
+      <c r="D53" s="99"/>
       <c r="E53" s="75"/>
       <c r="F53" s="76"/>
       <c r="G53" s="36">
@@ -4260,12 +4260,12 @@
       <c r="AD53" s="39"/>
     </row>
     <row r="54" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A54" s="97"/>
-      <c r="B54" s="98"/>
-      <c r="C54" s="103" t="s">
+      <c r="A54" s="100"/>
+      <c r="B54" s="99"/>
+      <c r="C54" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="D54" s="98"/>
+      <c r="D54" s="99"/>
       <c r="E54" s="77"/>
       <c r="F54" s="78"/>
       <c r="G54" s="36">
@@ -4298,82 +4298,82 @@
       <c r="AD54" s="81"/>
     </row>
     <row r="55" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A55" s="104" t="s">
+      <c r="A55" s="169" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="105"/>
-      <c r="C55" s="105"/>
-      <c r="D55" s="105"/>
-      <c r="E55" s="98"/>
+      <c r="B55" s="153"/>
+      <c r="C55" s="153"/>
+      <c r="D55" s="153"/>
+      <c r="E55" s="99"/>
       <c r="F55" s="82"/>
       <c r="G55" s="83"/>
       <c r="H55" s="83"/>
       <c r="I55" s="82"/>
-      <c r="J55" s="129"/>
-      <c r="K55" s="130"/>
-      <c r="L55" s="130"/>
-      <c r="M55" s="130"/>
-      <c r="N55" s="130"/>
-      <c r="O55" s="130"/>
-      <c r="P55" s="130"/>
-      <c r="Q55" s="130"/>
-      <c r="R55" s="130"/>
-      <c r="S55" s="130"/>
-      <c r="T55" s="130"/>
-      <c r="U55" s="130"/>
-      <c r="V55" s="130"/>
-      <c r="W55" s="130"/>
-      <c r="X55" s="130"/>
-      <c r="Y55" s="130"/>
-      <c r="Z55" s="130"/>
-      <c r="AA55" s="130"/>
-      <c r="AB55" s="130"/>
-      <c r="AC55" s="130"/>
-      <c r="AD55" s="130"/>
+      <c r="J55" s="139"/>
+      <c r="K55" s="140"/>
+      <c r="L55" s="140"/>
+      <c r="M55" s="140"/>
+      <c r="N55" s="140"/>
+      <c r="O55" s="140"/>
+      <c r="P55" s="140"/>
+      <c r="Q55" s="140"/>
+      <c r="R55" s="140"/>
+      <c r="S55" s="140"/>
+      <c r="T55" s="140"/>
+      <c r="U55" s="140"/>
+      <c r="V55" s="140"/>
+      <c r="W55" s="140"/>
+      <c r="X55" s="140"/>
+      <c r="Y55" s="140"/>
+      <c r="Z55" s="140"/>
+      <c r="AA55" s="140"/>
+      <c r="AB55" s="140"/>
+      <c r="AC55" s="140"/>
+      <c r="AD55" s="140"/>
     </row>
     <row r="56" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
       <c r="A56" s="32"/>
       <c r="B56" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="106" t="s">
+      <c r="C56" s="152" t="s">
         <v>67</v>
       </c>
-      <c r="D56" s="105"/>
-      <c r="E56" s="105"/>
-      <c r="F56" s="105"/>
-      <c r="G56" s="105"/>
-      <c r="H56" s="105"/>
-      <c r="I56" s="98"/>
-      <c r="J56" s="112"/>
-      <c r="K56" s="113"/>
-      <c r="L56" s="113"/>
-      <c r="M56" s="113"/>
-      <c r="N56" s="113"/>
-      <c r="O56" s="113"/>
-      <c r="P56" s="113"/>
-      <c r="Q56" s="113"/>
-      <c r="R56" s="113"/>
-      <c r="S56" s="113"/>
-      <c r="T56" s="113"/>
-      <c r="U56" s="113"/>
-      <c r="V56" s="113"/>
-      <c r="W56" s="113"/>
-      <c r="X56" s="113"/>
-      <c r="Y56" s="113"/>
-      <c r="Z56" s="113"/>
-      <c r="AA56" s="113"/>
-      <c r="AB56" s="113"/>
-      <c r="AC56" s="113"/>
-      <c r="AD56" s="113"/>
+      <c r="D56" s="153"/>
+      <c r="E56" s="153"/>
+      <c r="F56" s="153"/>
+      <c r="G56" s="153"/>
+      <c r="H56" s="153"/>
+      <c r="I56" s="99"/>
+      <c r="J56" s="141"/>
+      <c r="K56" s="142"/>
+      <c r="L56" s="142"/>
+      <c r="M56" s="142"/>
+      <c r="N56" s="142"/>
+      <c r="O56" s="142"/>
+      <c r="P56" s="142"/>
+      <c r="Q56" s="142"/>
+      <c r="R56" s="142"/>
+      <c r="S56" s="142"/>
+      <c r="T56" s="142"/>
+      <c r="U56" s="142"/>
+      <c r="V56" s="142"/>
+      <c r="W56" s="142"/>
+      <c r="X56" s="142"/>
+      <c r="Y56" s="142"/>
+      <c r="Z56" s="142"/>
+      <c r="AA56" s="142"/>
+      <c r="AB56" s="142"/>
+      <c r="AC56" s="142"/>
+      <c r="AD56" s="142"/>
     </row>
     <row r="57" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A57" s="97"/>
-      <c r="B57" s="98"/>
-      <c r="C57" s="99" t="s">
+      <c r="A57" s="100"/>
+      <c r="B57" s="99"/>
+      <c r="C57" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="98"/>
+      <c r="D57" s="99"/>
       <c r="E57" s="63"/>
       <c r="F57" s="37" t="s">
         <v>86</v>
@@ -4406,10 +4406,10 @@
     <row r="58" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
       <c r="A58" s="86"/>
       <c r="B58" s="87"/>
-      <c r="C58" s="99" t="s">
+      <c r="C58" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="D58" s="98"/>
+      <c r="D58" s="99"/>
       <c r="E58" s="88"/>
       <c r="F58" s="37" t="s">
         <v>86</v>
@@ -4440,12 +4440,12 @@
       <c r="AD58" s="89"/>
     </row>
     <row r="59" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A59" s="97"/>
-      <c r="B59" s="98"/>
-      <c r="C59" s="100" t="s">
+      <c r="A59" s="100"/>
+      <c r="B59" s="99"/>
+      <c r="C59" s="173" t="s">
         <v>70</v>
       </c>
-      <c r="D59" s="101"/>
+      <c r="D59" s="174"/>
       <c r="E59" s="90"/>
       <c r="F59" s="37" t="s">
         <v>86</v>
@@ -4476,12 +4476,12 @@
       <c r="AD59" s="41"/>
     </row>
     <row r="60" spans="1:30" s="23" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A60" s="97"/>
-      <c r="B60" s="98"/>
-      <c r="C60" s="100" t="s">
+      <c r="A60" s="100"/>
+      <c r="B60" s="99"/>
+      <c r="C60" s="173" t="s">
         <v>71</v>
       </c>
-      <c r="D60" s="101"/>
+      <c r="D60" s="174"/>
       <c r="E60" s="90"/>
       <c r="F60" s="37" t="s">
         <v>86</v>
@@ -33076,27 +33076,87 @@
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="A8:I9"/>
-    <mergeCell ref="J8:Z8"/>
-    <mergeCell ref="AA8:AD8"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="N9:R9"/>
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="C56:I56"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="J26:AD26"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="D10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:I41"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="J55:AD55"/>
+    <mergeCell ref="J56:AD56"/>
+    <mergeCell ref="J12:AD12"/>
+    <mergeCell ref="J13:AD13"/>
+    <mergeCell ref="J16:AD16"/>
+    <mergeCell ref="J18:AD18"/>
+    <mergeCell ref="J19:AD19"/>
+    <mergeCell ref="J21:AD21"/>
+    <mergeCell ref="J25:AD25"/>
     <mergeCell ref="AE10:AE11"/>
     <mergeCell ref="AA10:AA11"/>
     <mergeCell ref="AB10:AB11"/>
@@ -33121,61 +33181,32 @@
     <mergeCell ref="U10:U11"/>
     <mergeCell ref="V10:V11"/>
     <mergeCell ref="Z10:Z11"/>
-    <mergeCell ref="J55:AD55"/>
-    <mergeCell ref="J56:AD56"/>
-    <mergeCell ref="J12:AD12"/>
-    <mergeCell ref="J13:AD13"/>
-    <mergeCell ref="J16:AD16"/>
-    <mergeCell ref="J18:AD18"/>
-    <mergeCell ref="J19:AD19"/>
-    <mergeCell ref="J21:AD21"/>
-    <mergeCell ref="J25:AD25"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="A8:I9"/>
+    <mergeCell ref="J8:Z8"/>
+    <mergeCell ref="AA8:AD8"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="N9:R9"/>
+    <mergeCell ref="AC9:AD9"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C46:I46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:I41"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:I52"/>
-    <mergeCell ref="B10:C11"/>
-    <mergeCell ref="D10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C42:D42"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
@@ -33183,37 +33214,6 @@
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="J26:AD26"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="C56:I56"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
